--- a/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
+++ b/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28BCEBB-9567-465C-BDDB-4D8E34D9559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
@@ -34,11 +33,11 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$158</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">krishi!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="102">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -352,14 +351,89 @@
   <si>
     <t xml:space="preserve">Date:                  </t>
   </si>
+  <si>
+    <t>-long wall</t>
+  </si>
+  <si>
+    <t>-deduction for 14" wall</t>
+  </si>
+  <si>
+    <t>- 14" wall</t>
+  </si>
+  <si>
+    <t>-short wall</t>
+  </si>
+  <si>
+    <t>e'O{+tNnfdf lrDgL e§fsf] O{+6fsf] uf/f] l;d]G6 d;nf -!M$_ df</t>
+  </si>
+  <si>
+    <r>
+      <t>%) dL=dL=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> X</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;% dL=dL= cu|fvsf] k|m]d ^)) dL=dL=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> X</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> ^)) dL=dL= df xfnL @% dL=dL= afSnf] cu|fvsf7sf] ˆn]s 5fKg] sfd</t>
+    </r>
+  </si>
+  <si>
+    <t>-13% VAT for killa kaanti</t>
+  </si>
+  <si>
+    <t>-13% VAT for agrakh kaath</t>
+  </si>
+  <si>
+    <t>kfs]6 lj5\ofpg] / vfS;L nufO{ kfln; ug]{ sfd</t>
+  </si>
+  <si>
+    <t>-flooring</t>
+  </si>
+  <si>
+    <t>-13% VAT for parquete</t>
+  </si>
+  <si>
+    <t>-13% VAT for main polish</t>
+  </si>
+  <si>
+    <t>-13% VAT for khakshi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -526,9 +600,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -544,14 +618,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -580,7 +654,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -617,7 +691,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -635,7 +709,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -644,9 +718,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -670,29 +759,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -708,7 +782,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -802,7 +876,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -861,7 +935,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -925,9 +999,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -965,9 +1039,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1002,7 +1076,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1037,7 +1111,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1210,7 +1284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M158"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1226,113 +1300,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4635,11 +4709,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="55">
+      <c r="C153" s="47">
         <f>J151</f>
         <v>520268.58119831659</v>
       </c>
-      <c r="D153" s="56"/>
+      <c r="D153" s="48"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4654,21 +4728,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="57">
+      <c r="C154" s="49">
         <v>700000</v>
       </c>
-      <c r="D154" s="58"/>
+      <c r="D154" s="50"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="57">
+      <c r="C155" s="49">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="58"/>
+      <c r="D155" s="50"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>127.81859678482381</v>
@@ -4678,11 +4752,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="59">
+      <c r="C156" s="51">
         <f>C153-C155</f>
         <v>-144731.41880168341</v>
       </c>
-      <c r="D156" s="59"/>
+      <c r="D156" s="51"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>-27.818596784823811</v>
@@ -4692,11 +4766,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="55">
+      <c r="C157" s="47">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="56"/>
+      <c r="D157" s="48"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -4705,23 +4779,17 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="55">
+      <c r="C158" s="47">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="56"/>
+      <c r="D158" s="48"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -4731,6 +4799,12 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -4741,13 +4815,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0208501D-94C1-43B5-8F9B-D23B4DCB59C4}">
-  <dimension ref="A1:K54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" customWidth="1"/>
@@ -4757,113 +4831,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4900,12 +4974,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="61.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>94</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="23"/>
@@ -4919,26 +4993,23 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
-      <c r="B10" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C10" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D10" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="B10" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="15">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <f>(272+272)/12/3.281</f>
+        <v>13.81692573402418</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3" t="e">
-        <f>#REF!-0.23</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G10" s="3" t="e">
+      <c r="F10" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G10" s="3">
         <f>PRODUCT(C10:F10)</f>
-        <v>#REF!</v>
+        <v>20.725388601036268</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
@@ -4947,254 +5018,193 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
-      <c r="B11" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C11" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D11" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="B11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="15">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <f>236/12/3.281</f>
+        <v>5.9941074875546079</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
-      </c>
-      <c r="G11" s="3" t="e">
-        <f>PRODUCT(C11:F11)</f>
-        <v>#REF!</v>
+        <v>0.75</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" ref="G11" si="0">PRODUCT(C11:F11)</f>
+        <v>8.9911612313319118</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C12" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D12" s="3">
-        <f>0.35*4</f>
-        <v>1.4</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G12" s="3" t="e">
-        <f t="shared" ref="G12:G18" si="0">PRODUCT(C12:F12)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C13" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D13" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
-      </c>
-      <c r="G13" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C14" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D14" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
-      </c>
-      <c r="G14" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
+    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="2">
+        <f>SUM(G10:G11)</f>
+        <v>29.71654983236818</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9949.51</v>
+      </c>
+      <c r="J12" s="22">
+        <f>G12*I12</f>
+        <v>295665.10972264555</v>
+      </c>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="22">
+        <f>0.13*G12*90530.95/10</f>
+        <v>34973.47733160622</v>
+      </c>
+      <c r="K13" s="26"/>
+    </row>
+    <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="22">
+        <f>0.13*G12*264/10</f>
+        <v>101.98719902468761</v>
+      </c>
+      <c r="K14" s="26"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
-      <c r="B15" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C15" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D15" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G15" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C16" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D16" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G16" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
+    <row r="16" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>2</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
-      <c r="B17" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C17" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D17" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E17" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="B17" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <f>35.083/3.281</f>
+        <v>10.692776592502286</v>
+      </c>
+      <c r="E17" s="3">
+        <f>236/12/3.281</f>
+        <v>5.9941074875546079</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
+      <c r="G17" s="3">
+        <f>PRODUCT(C17:F17)</f>
+        <v>64.0936522358666</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="15" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D18" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E18" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18" t="s">
+    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="2" t="e">
-        <f>0*SUM(G10:G18)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H19" s="21" t="s">
+      <c r="C18" s="19"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="2">
+        <f>SUM(G17:G17)</f>
+        <v>64.0936522358666</v>
+      </c>
+      <c r="H18" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="2">
-        <v>922.71</v>
-      </c>
-      <c r="J19" s="22" t="e">
-        <f>G19*I19</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K19" s="20"/>
+      <c r="I18" s="2">
+        <v>2808.56</v>
+      </c>
+      <c r="J18" s="22">
+        <f>G18*I18</f>
+        <v>180010.8679235655</v>
+      </c>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="22">
+        <f>0.13*G18*24855.6/10</f>
+        <v>20710.120372679477</v>
+      </c>
+      <c r="K19" s="26"/>
     </row>
     <row r="20" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="27"/>
@@ -5203,16 +5213,16 @@
       <c r="G20" s="27"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="22" t="e">
-        <f>0.13*G19*20062.02/100</f>
-        <v>#REF!</v>
+      <c r="J20" s="22">
+        <f>0.13*G18*50/10</f>
+        <v>41.660873953313299</v>
       </c>
       <c r="K20" s="26"/>
     </row>
     <row r="21" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24"/>
       <c r="B21" s="25" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="27"/>
@@ -5221,73 +5231,93 @@
       <c r="G21" s="27"/>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="22" t="e">
-        <f>0.13*G19*13328.25/100</f>
-        <v>#REF!</v>
+      <c r="J21" s="22">
+        <f>0.13*G18*300/10</f>
+        <v>249.96524371987977</v>
       </c>
       <c r="K21" s="26"/>
     </row>
-    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="22" t="e">
-        <f>0.13*G19*10137.6/100</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K22" s="26"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="25" t="s">
-        <v>50</v>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>3</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="C23" s="15"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
-      <c r="J23" s="22" t="e">
-        <f>0.13*G19*3300/100</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J23" s="15"/>
       <c r="K23" s="15"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="B24" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3">
+        <f>(48.5/3.281)</f>
+        <v>14.782078634562632</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F24" s="3">
+        <f>2.75/3.281</f>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G24" s="3">
+        <f>PRODUCT(C24:F24)</f>
+        <v>5.6992774985436547</v>
+      </c>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
-        <v>10</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="3">
+        <f>-5*2</f>
+        <v>-10</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F25" s="3">
+        <f>2.75/3.281</f>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" ref="G25" si="1">PRODUCT(C25:F25)</f>
+        <v>-0.67471807375800064</v>
+      </c>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
@@ -5295,27 +5325,26 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
-      <c r="B26" s="16" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C26" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D26" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="B26" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="3">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.35</v>
       </c>
       <c r="E26" s="3">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="F26" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="G26" s="3" t="e">
-        <f t="shared" ref="G26:G31" si="1">PRODUCT(C26:F26)</f>
-        <v>#REF!</v>
+        <f>2.75/3.281</f>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" ref="G26" si="2">PRODUCT(C26:F26)</f>
+        <v>1.0267448948491313</v>
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
@@ -5325,25 +5354,25 @@
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
       <c r="B27" s="16" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C27" s="3">
         <v>2</v>
       </c>
       <c r="D27" s="3">
-        <f>18.5/3.281</f>
-        <v>5.6385248399878085</v>
+        <f>((21.5-1.25*3)/3.281)</f>
+        <v>5.4099359951234378</v>
       </c>
       <c r="E27" s="3">
         <v>0.23</v>
       </c>
       <c r="F27" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
+        <f>2.75/3.281</f>
+        <v>0.8381590978360256</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="1"/>
-        <v>5.9289578475946181</v>
+        <f>PRODUCT(C27:F27)</f>
+        <v>2.0858180535907187</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
@@ -5352,24 +5381,25 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>91</v>
+      </c>
       <c r="C28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3">
-        <f>(8.75+17.5)/3.281</f>
-        <v>8.0006095702529709</v>
+        <v>0.35</v>
       </c>
       <c r="E28" s="3">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="F28" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
+        <f>2.75/3.281</f>
+        <v>0.8381590978360256</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="1"/>
-        <v>8.4127104594247939</v>
+        <f>PRODUCT(C28:F28)</f>
+        <v>0.10267448948491312</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
@@ -5379,116 +5409,97 @@
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="16" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3">
-        <v>1</v>
+        <f>-5*2</f>
+        <v>-10</v>
       </c>
       <c r="D29" s="3">
-        <f>D28</f>
-        <v>8.0006095702529709</v>
+        <v>0.35</v>
       </c>
       <c r="E29" s="3">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="F29" s="3">
-        <v>0.45</v>
+        <f>2.75/3.281</f>
+        <v>0.8381590978360256</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="1"/>
-        <v>1.0800822919841511</v>
+        <f t="shared" ref="G29" si="3">PRODUCT(C29:F29)</f>
+        <v>-0.67471807375800064</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="3">
-        <v>-2</v>
-      </c>
-      <c r="D30" s="3">
-        <f>1.8</f>
-        <v>1.8</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F30" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G30" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.1356293812861933</v>
-      </c>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F31" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G31" s="3">
-        <f t="shared" si="1"/>
-        <v>-0.76916209914740985</v>
-      </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="18" t="s">
+    <row r="30" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="2" t="e">
-        <f>SUM(G26:G31)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H32" s="21" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="2">
+        <f>SUM(G24:G29)</f>
+        <v>7.565078788952416</v>
+      </c>
+      <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I30" s="2">
         <f>14491.84</f>
         <v>14491.84</v>
       </c>
-      <c r="J32" s="22" t="e">
-        <f>G32*I32</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K32" s="20"/>
+      <c r="J30" s="22">
+        <f>G30*I30</f>
+        <v>109631.91139689219</v>
+      </c>
+      <c r="K30" s="20"/>
+    </row>
+    <row r="31" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="22">
+        <f>0.13*G30*8481.2</f>
+        <v>8340.9230092322214</v>
+      </c>
+      <c r="K31" s="26"/>
+    </row>
+    <row r="32" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="22">
+        <f>0.13*G30*912.17</f>
+        <v>897.08292945943435</v>
+      </c>
+      <c r="K32" s="26"/>
     </row>
     <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
       <c r="B33" s="25" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="27"/>
@@ -5497,16 +5508,16 @@
       <c r="G33" s="27"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="22" t="e">
-        <f>0.13*G32*8481.2</f>
-        <v>#REF!</v>
+      <c r="J33" s="22">
+        <f>0.13*G30*953.37</f>
+        <v>937.60149145306355</v>
       </c>
       <c r="K33" s="26"/>
     </row>
     <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
       <c r="B34" s="25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="27"/>
@@ -5515,17 +5526,15 @@
       <c r="G34" s="27"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="22" t="e">
-        <f>0.13*G32*912.17</f>
-        <v>#REF!</v>
+      <c r="J34" s="22">
+        <f>0.13*G30*28</f>
+        <v>27.536886791786795</v>
       </c>
       <c r="K34" s="26"/>
     </row>
     <row r="35" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
-      <c r="B35" s="25" t="s">
-        <v>64</v>
-      </c>
+      <c r="B35" s="25"/>
       <c r="C35" s="26"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
@@ -5533,114 +5542,120 @@
       <c r="G35" s="27"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="22" t="e">
-        <f>0.13*G32*953.37</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J35" s="22"/>
       <c r="K35" s="26"/>
     </row>
-    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="22" t="e">
-        <f>0.13*G32*28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K36" s="26"/>
+    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
+        <v>4</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
+      <c r="B37" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D37" s="3">
+        <f>11.33/3.281</f>
+        <v>3.4532154830844255</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F37" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G37" s="3">
+        <f>PRODUCT(C37:F37)</f>
+        <v>1.4734842049125862</v>
+      </c>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
     </row>
-    <row r="38" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="24">
-        <v>13</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="26"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
-      <c r="B39" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="3">
-        <v>2</v>
-      </c>
-      <c r="D39" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G39" s="3">
-        <f>PRODUCT(C39:F39)</f>
-        <v>4.9375190490704055</v>
-      </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="18" t="s">
+    <row r="38" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="2">
-        <f>SUM(G38:G39)</f>
-        <v>4.9375190490704055</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I40" s="2">
-        <v>2485.56</v>
-      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="2">
+        <f>SUM(G37:G37)</f>
+        <v>1.4734842049125862</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="2">
+        <v>14827.62</v>
+      </c>
+      <c r="J38" s="22">
+        <f>G38*I38</f>
+        <v>21848.263866445963</v>
+      </c>
+      <c r="K38" s="20"/>
+    </row>
+    <row r="39" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="26"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="22">
+        <f>0.13*G38*8481.2</f>
+        <v>1624.5988510316017</v>
+      </c>
+      <c r="K39" s="26"/>
+    </row>
+    <row r="40" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
       <c r="J40" s="22">
-        <f>G40*I40</f>
-        <v>12272.499847607436</v>
-      </c>
-      <c r="K40" s="20"/>
+        <f>0.13*G38*1303.1</f>
+        <v>249.61264476480684</v>
+      </c>
+      <c r="K40" s="26"/>
     </row>
     <row r="41" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24"/>
       <c r="B41" s="25" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="27"/>
@@ -5650,14 +5665,16 @@
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
       <c r="J41" s="22">
-        <f>0.13*J40</f>
-        <v>1595.4249801889669</v>
+        <f>0.13*G38*889.81</f>
+        <v>170.44572744852491</v>
       </c>
       <c r="K41" s="26"/>
     </row>
     <row r="42" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="24"/>
-      <c r="B42" s="25"/>
+      <c r="B42" s="25" t="s">
+        <v>36</v>
+      </c>
       <c r="C42" s="26"/>
       <c r="D42" s="27"/>
       <c r="E42" s="27"/>
@@ -5665,213 +5682,187 @@
       <c r="G42" s="27"/>
       <c r="H42" s="26"/>
       <c r="I42" s="26"/>
-      <c r="J42" s="22"/>
+      <c r="J42" s="22">
+        <f>0.13*G38*36.4</f>
+        <v>6.9725272576463588</v>
+      </c>
       <c r="K42" s="26"/>
     </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17">
-        <v>14</v>
-      </c>
-      <c r="B43" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="19">
+    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="26"/>
+    </row>
+    <row r="44" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
+        <v>15</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="19">
         <v>1</v>
       </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="21">
-        <f t="shared" ref="G43" si="2">PRODUCT(C43:F43)</f>
-        <v>1</v>
-      </c>
-      <c r="H43" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J43" s="21">
-        <f>G43*I43</f>
-        <v>5000</v>
-      </c>
-      <c r="K43" s="20"/>
-    </row>
-    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="19"/>
       <c r="D44" s="1"/>
       <c r="E44" s="20"/>
       <c r="F44" s="20"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="22"/>
+      <c r="G44" s="21">
+        <f t="shared" ref="G44" si="4">PRODUCT(C44:F44)</f>
+        <v>1</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="2">
+        <v>500</v>
+      </c>
+      <c r="J44" s="21">
+        <f>G44*I44</f>
+        <v>500</v>
+      </c>
       <c r="K44" s="20"/>
     </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17">
-        <v>15</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="19">
-        <v>1</v>
-      </c>
+    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="19"/>
       <c r="D45" s="1"/>
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
-      <c r="G45" s="21">
-        <f t="shared" ref="G45" si="3">PRODUCT(C45:F45)</f>
-        <v>1</v>
-      </c>
-      <c r="H45" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="2">
-        <v>500</v>
-      </c>
-      <c r="J45" s="21">
-        <f>G45*I45</f>
-        <v>500</v>
-      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="22"/>
       <c r="K45" s="20"/>
     </row>
     <row r="46" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="20"/>
-    </row>
-    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="32"/>
-      <c r="B47" s="33" t="s">
+      <c r="A46" s="32"/>
+      <c r="B46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="34"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22" t="e">
-        <f>SUM(J9:J45)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K47" s="36"/>
-    </row>
-    <row r="48" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="37"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22">
+        <f>SUM(J9:J44)</f>
+        <v>675988.13799797196</v>
+      </c>
+      <c r="K46" s="36"/>
+    </row>
+    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="37"/>
+      <c r="B48" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="47">
+        <f>J46</f>
+        <v>675988.13799797196</v>
+      </c>
+      <c r="D48" s="48"/>
+      <c r="E48" s="39">
+        <v>100</v>
+      </c>
+      <c r="F48" s="37"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="55" t="e">
-        <f>J47</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D49" s="56"/>
-      <c r="E49" s="39">
-        <v>100</v>
-      </c>
-      <c r="F49" s="37"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="42"/>
-      <c r="K49" s="43"/>
-    </row>
-    <row r="50" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="C49" s="49">
+        <v>700000</v>
+      </c>
+      <c r="D49" s="50"/>
+      <c r="E49" s="39"/>
+    </row>
+    <row r="50" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="57">
-        <v>700000</v>
-      </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="39"/>
-    </row>
-    <row r="51" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="C50" s="49">
+        <f>C49-C52-C53</f>
+        <v>665000</v>
+      </c>
+      <c r="D50" s="50"/>
+      <c r="E50" s="39">
+        <f>C50/C48*100</f>
+        <v>98.374507276042621</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" s="57">
-        <f>C50-C53-C54</f>
-        <v>665000</v>
-      </c>
-      <c r="D51" s="58"/>
-      <c r="E51" s="39" t="e">
-        <f>C51/C49*100</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="C51" s="51">
+        <f>C48-C50</f>
+        <v>10988.137997971964</v>
+      </c>
+      <c r="D51" s="51"/>
+      <c r="E51" s="39">
+        <f>100-E50</f>
+        <v>1.6254927239573789</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="59" t="e">
-        <f>C49-C51</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D52" s="59"/>
-      <c r="E52" s="39" t="e">
-        <f>100-E51</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="C52" s="47">
+        <f>C49*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D52" s="48"/>
+      <c r="E52" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" s="55">
-        <f>C50*0.03</f>
-        <v>21000</v>
-      </c>
-      <c r="D53" s="56"/>
+        <v>24</v>
+      </c>
+      <c r="C53" s="47">
+        <f>C49*0.02</f>
+        <v>14000</v>
+      </c>
+      <c r="D53" s="48"/>
       <c r="E53" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="55">
-        <f>C50*0.02</f>
-        <v>14000</v>
-      </c>
-      <c r="D54" s="56"/>
-      <c r="E54" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>

--- a/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
+++ b/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5618C2-409A-4CC4-B70D-27F9F5D3E684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
@@ -33,11 +34,11 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$158</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$97</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">krishi!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="125">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -426,16 +427,239 @@
   <si>
     <t>-13% VAT for khakshi</t>
   </si>
+  <si>
+    <t>-outer face of wall</t>
+  </si>
+  <si>
+    <t>-inner face of wall</t>
+  </si>
+  <si>
+    <t>-as of plaster</t>
+  </si>
+  <si>
+    <t>ljleGg ;fO{hsf] kmnfd] PËn km]lj|s]zg u/L k|fOd/ k]G6 ;lxt ug]{ sfd</t>
+  </si>
+  <si>
+    <t>Unit weight (Kg/m)</t>
+  </si>
+  <si>
+    <t>Weight (Kg)</t>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t>-MS square pipe for post of 75mm*75mm*5mm thickness</t>
+  </si>
+  <si>
+    <t>-75mm*75mm*5mm size equal angle for stage binding</t>
+  </si>
+  <si>
+    <t>-at stage</t>
+  </si>
+  <si>
+    <t>-13% VAT for any kind of angles and MS black pipes</t>
+  </si>
+  <si>
+    <t>-13% VAT for primer</t>
+  </si>
+  <si>
+    <t>-deduction for stage area</t>
+  </si>
+  <si>
+    <r>
+      <t>%) dL=dL=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Ø</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> sf] sfnf] kmnfd] kfO{k kf]i6 @ dL6/ b"/Ldf</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve">@% </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> @% </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> $ dL=dL= ;fO{hsf] kmnfd] PËn k|m]ddf &amp; dL=dL=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ø</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> kmnfd] 808Lsf] 8fouf]gnL hfnL ^@ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> ^@ dL=dL= ;fOhdf h8fg ug]{ / #</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>@) sf] kmnfd] kftfsf] lu|n )=!% dL= cUnf] agfO{ dfly h8fg u/L km]lj|s]zg u/L k|fOd/ k]G6 ;lxt ;Dk"0f{ sfo{ .</t>
+    </r>
+  </si>
+  <si>
+    <t>-fencing</t>
+  </si>
+  <si>
+    <t>-13% VAT for 50mm Ø post</t>
+  </si>
+  <si>
+    <t>-13% VAT for 25mm*25mm*4mm angle</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">-13% VAT for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>kmnfd] kftfsf] lu|n #</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>@) dL=dL=</t>
+    </r>
+  </si>
+  <si>
+    <t>-13% VAT for 7mm steel rod</t>
+  </si>
+  <si>
+    <t>-partition wall</t>
+  </si>
+  <si>
+    <t>- 9" wall</t>
+  </si>
+  <si>
+    <t>Provisional sum for unforseen work</t>
+  </si>
+  <si>
+    <r>
+      <t>Project:-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> s[lif pkh ;+sng s]Gb| lgdf{0f</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,6 +754,10 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Preeti"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -600,13 +828,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -618,14 +846,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -654,7 +882,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -691,7 +919,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -709,7 +937,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -718,27 +946,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -753,20 +968,54 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -782,7 +1031,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -876,7 +1125,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -935,7 +1184,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -999,9 +1248,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1039,9 +1288,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1076,7 +1325,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1111,7 +1360,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1284,7 +1533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M158"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1300,113 +1549,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4709,11 +4958,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="47">
+      <c r="C153" s="53">
         <f>J151</f>
         <v>520268.58119831659</v>
       </c>
-      <c r="D153" s="48"/>
+      <c r="D153" s="54"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4728,21 +4977,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="49">
+      <c r="C154" s="57">
         <v>700000</v>
       </c>
-      <c r="D154" s="50"/>
+      <c r="D154" s="58"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="49">
+      <c r="C155" s="57">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="50"/>
+      <c r="D155" s="58"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>127.81859678482381</v>
@@ -4752,11 +5001,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="51">
+      <c r="C156" s="59">
         <f>C153-C155</f>
         <v>-144731.41880168341</v>
       </c>
-      <c r="D156" s="51"/>
+      <c r="D156" s="59"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>-27.818596784823811</v>
@@ -4766,11 +5015,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="47">
+      <c r="C157" s="53">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="48"/>
+      <c r="D157" s="54"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -4779,17 +5028,23 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="47">
+      <c r="C158" s="53">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="48"/>
+      <c r="D158" s="54"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -4799,12 +5054,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -4815,11 +5064,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" style="14" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" customWidth="1"/>
     <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
@@ -4827,120 +5076,120 @@
     <col min="6" max="6" width="7.28515625" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="A6" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="60" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -4992,7 +5241,7 @@
       <c r="K9" s="13"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
         <v>89</v>
       </c>
@@ -5017,7 +5266,7 @@
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="16" t="s">
         <v>92</v>
       </c>
@@ -5033,7 +5282,7 @@
         <v>0.75</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" ref="G11" si="0">PRODUCT(C11:F11)</f>
+        <f t="shared" ref="G11:G13" si="0">PRODUCT(C11:F11)</f>
         <v>8.9911612313319118</v>
       </c>
       <c r="H11" s="15"/>
@@ -5041,365 +5290,354 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="15">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <f>28.75/3.281</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E12" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <f t="shared" si="0"/>
+        <v>18.027236698767414</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <f>32.25/3.281</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E13" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>20.221856818617361</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="2">
-        <f>SUM(G10:G11)</f>
-        <v>29.71654983236818</v>
-      </c>
-      <c r="H12" s="21" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="2">
+        <f>SUM(G10:G13)</f>
+        <v>67.965643349752952</v>
+      </c>
+      <c r="H14" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I14" s="2">
         <v>9949.51</v>
       </c>
-      <c r="J12" s="22">
-        <f>G12*I12</f>
-        <v>295665.10972264555</v>
-      </c>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25" t="s">
+      <c r="J14" s="22">
+        <f>G14*I14</f>
+        <v>676224.84816480055</v>
+      </c>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="22">
-        <f>0.13*G12*90530.95/10</f>
-        <v>34973.47733160622</v>
-      </c>
-      <c r="K13" s="26"/>
-    </row>
-    <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25" t="s">
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="22">
+        <f>0.13*G14*90530.95/10</f>
+        <v>79988.925377586129</v>
+      </c>
+      <c r="K15" s="26"/>
+    </row>
+    <row r="16" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="22">
-        <f>0.13*G12*264/10</f>
-        <v>101.98719902468761</v>
-      </c>
-      <c r="K14" s="26"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
-        <v>2</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="22">
+        <f>0.13*G14*264/10</f>
+        <v>233.25808797635213</v>
+      </c>
+      <c r="K16" s="26"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <f>35.083/3.281</f>
-        <v>10.692776592502286</v>
-      </c>
-      <c r="E17" s="3">
-        <f>236/12/3.281</f>
-        <v>5.9941074875546079</v>
-      </c>
+      <c r="A17" s="13"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3">
-        <f>PRODUCT(C17:F17)</f>
-        <v>64.0936522358666</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18" t="s">
+    <row r="18" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>2</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <f>35.083/3.281</f>
+        <v>10.692776592502286</v>
+      </c>
+      <c r="E19" s="3">
+        <f>236/12/3.281</f>
+        <v>5.9941074875546079</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3">
+        <f>PRODUCT(C19:F19)</f>
+        <v>64.0936522358666</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="15">
+        <v>-1</v>
+      </c>
+      <c r="D20" s="3">
+        <f>D12</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E20" s="3">
+        <f>E12</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3">
+        <f t="shared" ref="G20:G21" si="1">PRODUCT(C20:F20)</f>
+        <v>-18.027236698767414</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="15">
+        <v>-1</v>
+      </c>
+      <c r="D21" s="3">
+        <f>D13</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E21" s="3">
+        <f>E13</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3">
+        <f t="shared" si="1"/>
+        <v>-20.221856818617361</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="2">
-        <f>SUM(G17:G17)</f>
-        <v>64.0936522358666</v>
-      </c>
-      <c r="H18" s="21" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="2">
+        <f>SUM(G19:G21)</f>
+        <v>25.844558718481828</v>
+      </c>
+      <c r="H22" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I22" s="2">
         <v>2808.56</v>
       </c>
-      <c r="J18" s="22">
-        <f>G18*I18</f>
-        <v>180010.8679235655</v>
-      </c>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25" t="s">
+      <c r="J22" s="22">
+        <f>G22*I22</f>
+        <v>72585.993834379318</v>
+      </c>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="22">
-        <f>0.13*G18*24855.6/10</f>
-        <v>20710.120372679477</v>
-      </c>
-      <c r="K19" s="26"/>
-    </row>
-    <row r="20" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="22">
+        <f>0.13*G22*24855.6/10</f>
+        <v>8350.9661778802583</v>
+      </c>
+      <c r="K23" s="26"/>
+    </row>
+    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="22">
-        <f>0.13*G18*50/10</f>
-        <v>41.660873953313299</v>
-      </c>
-      <c r="K20" s="26"/>
-    </row>
-    <row r="21" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25" t="s">
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="22">
+        <f>0.13*G22*50/10</f>
+        <v>16.798963167013188</v>
+      </c>
+      <c r="K24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="22">
-        <f>0.13*G18*300/10</f>
-        <v>249.96524371987977</v>
-      </c>
-      <c r="K21" s="26"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-    </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <v>3</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="3">
-        <v>2</v>
-      </c>
-      <c r="D24" s="3">
-        <f>(48.5/3.281)</f>
-        <v>14.782078634562632</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F24" s="3">
-        <f>2.75/3.281</f>
-        <v>0.8381590978360256</v>
-      </c>
-      <c r="G24" s="3">
-        <f>PRODUCT(C24:F24)</f>
-        <v>5.6992774985436547</v>
-      </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="3">
-        <f>-5*2</f>
-        <v>-10</v>
-      </c>
-      <c r="D25" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F25" s="3">
-        <f>2.75/3.281</f>
-        <v>0.8381590978360256</v>
-      </c>
-      <c r="G25" s="3">
-        <f t="shared" ref="G25" si="1">PRODUCT(C25:F25)</f>
-        <v>-0.67471807375800064</v>
-      </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="22">
+        <f>0.13*G22*300/10</f>
+        <v>100.79377900207912</v>
+      </c>
+      <c r="K25" s="26"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="3">
-        <f>5*2</f>
-        <v>10</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F26" s="3">
-        <f>2.75/3.281</f>
-        <v>0.8381590978360256</v>
-      </c>
-      <c r="G26" s="3">
-        <f t="shared" ref="G26" si="2">PRODUCT(C26:F26)</f>
-        <v>1.0267448948491313</v>
-      </c>
+      <c r="A26" s="13"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="3">
-        <v>2</v>
-      </c>
-      <c r="D27" s="3">
-        <f>((21.5-1.25*3)/3.281)</f>
-        <v>5.4099359951234378</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F27" s="3">
-        <f>2.75/3.281</f>
-        <v>0.8381590978360256</v>
-      </c>
-      <c r="G27" s="3">
-        <f>PRODUCT(C27:F27)</f>
-        <v>2.0858180535907187</v>
-      </c>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>3</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3">
-        <v>0.35</v>
+        <f>(48.5/3.281)</f>
+        <v>14.782078634562632</v>
       </c>
       <c r="E28" s="3">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="F28" s="3">
-        <f>2.75/3.281</f>
+        <f t="shared" ref="F28:F30" si="2">2.75/3.281</f>
         <v>0.8381590978360256</v>
       </c>
       <c r="G28" s="3">
         <f>PRODUCT(C28:F28)</f>
-        <v>0.10267448948491312</v>
+        <v>5.6992774985436547</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
@@ -5407,7 +5645,7 @@
       <c r="K28" s="15"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="13"/>
       <c r="B29" s="16" t="s">
         <v>90</v>
       </c>
@@ -5422,7 +5660,7 @@
         <v>0.23</v>
       </c>
       <c r="F29" s="3">
-        <f>2.75/3.281</f>
+        <f t="shared" si="2"/>
         <v>0.8381590978360256</v>
       </c>
       <c r="G29" s="3">
@@ -5434,90 +5672,119 @@
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
     </row>
-    <row r="30" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="18" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="13"/>
+      <c r="B30" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="3">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" ref="G30" si="4">PRODUCT(C30:F30)</f>
+        <v>1.0267448948491313</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <f>((19.17-0.75)/3.281)</f>
+        <v>5.6141420298689431</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F31" s="3">
+        <f>(7.5+2.75)/3.281</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G31" s="3">
+        <f>PRODUCT(C31:F31)</f>
+        <v>1.7538846634000815</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F32" s="3">
+        <f>(7.5+2.75)/3.281</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G32" s="3">
+        <f>PRODUCT(C32:F32)</f>
+        <v>0.16526211520877782</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="2">
-        <f>SUM(G24:G29)</f>
-        <v>7.565078788952416</v>
-      </c>
-      <c r="H30" s="21" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="2">
+        <f>SUM(G28:G32)</f>
+        <v>7.9704510982436449</v>
+      </c>
+      <c r="H33" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I33" s="2">
         <f>14491.84</f>
         <v>14491.84</v>
       </c>
-      <c r="J30" s="22">
-        <f>G30*I30</f>
-        <v>109631.91139689219</v>
-      </c>
-      <c r="K30" s="20"/>
-    </row>
-    <row r="31" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="22">
-        <f>0.13*G30*8481.2</f>
-        <v>8340.9230092322214</v>
-      </c>
-      <c r="K31" s="26"/>
-    </row>
-    <row r="32" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="22">
-        <f>0.13*G30*912.17</f>
-        <v>897.08292945943435</v>
-      </c>
-      <c r="K32" s="26"/>
-    </row>
-    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
       <c r="J33" s="22">
-        <f>0.13*G30*953.37</f>
-        <v>937.60149145306355</v>
-      </c>
-      <c r="K33" s="26"/>
+        <f>G33*I33</f>
+        <v>115506.50204357118</v>
+      </c>
+      <c r="K33" s="20"/>
     </row>
     <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
       <c r="B34" s="25" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="27"/>
@@ -5527,14 +5794,16 @@
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
       <c r="J34" s="22">
-        <f>0.13*G30*28</f>
-        <v>27.536886791786795</v>
+        <f>0.13*G33*8481.2</f>
+        <v>8787.8686810751205</v>
       </c>
       <c r="K34" s="26"/>
     </row>
     <row r="35" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
+      <c r="B35" s="25" t="s">
+        <v>32</v>
+      </c>
       <c r="C35" s="26"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
@@ -5542,155 +5811,162 @@
       <c r="G35" s="27"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="22"/>
+      <c r="J35" s="22">
+        <f>0.13*G33*912.17</f>
+        <v>945.15282917703769</v>
+      </c>
       <c r="K35" s="26"/>
     </row>
-    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
+    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+      <c r="B36" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="22">
+        <f>0.13*G33*953.37</f>
+        <v>987.8425652592307</v>
+      </c>
+      <c r="K36" s="26"/>
+    </row>
+    <row r="37" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="22">
+        <f>0.13*G33*28</f>
+        <v>29.012441997606867</v>
+      </c>
+      <c r="K37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
         <v>4</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B39" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
-      <c r="B37" s="16" t="s">
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="13"/>
+      <c r="B40" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C40" s="3">
         <f>2*2</f>
         <v>4</v>
       </c>
-      <c r="D37" s="3">
-        <f>11.33/3.281</f>
-        <v>3.4532154830844255</v>
-      </c>
-      <c r="E37" s="3">
+      <c r="D40" s="3">
+        <f>(11.33-0.75)/3.281</f>
+        <v>3.2246266382200548</v>
+      </c>
+      <c r="E40" s="3">
         <v>0.1</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F40" s="3">
         <f>3.5/3.281</f>
         <v>1.0667479427003961</v>
       </c>
-      <c r="G37" s="3">
-        <f>PRODUCT(C37:F37)</f>
-        <v>1.4734842049125862</v>
-      </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-    </row>
-    <row r="38" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="18" t="s">
+      <c r="G40" s="3">
+        <f>PRODUCT(C40:F40)</f>
+        <v>1.3759455329192551</v>
+      </c>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="3">
+        <v>2</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F41" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G41" s="3">
+        <f>PRODUCT(C41:F41)</f>
+        <v>0.11286193233770191</v>
+      </c>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+    </row>
+    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="2">
-        <f>SUM(G37:G37)</f>
-        <v>1.4734842049125862</v>
-      </c>
-      <c r="H38" s="21" t="s">
+      <c r="C42" s="19"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="2">
+        <f>SUM(G40:G41)</f>
+        <v>1.488807465256957</v>
+      </c>
+      <c r="H42" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I42" s="2">
         <v>14827.62</v>
       </c>
-      <c r="J38" s="22">
-        <f>G38*I38</f>
-        <v>21848.263866445963</v>
-      </c>
-      <c r="K38" s="20"/>
-    </row>
-    <row r="39" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="22">
-        <f>0.13*G38*8481.2</f>
-        <v>1624.5988510316017</v>
-      </c>
-      <c r="K39" s="26"/>
-    </row>
-    <row r="40" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="22">
-        <f>0.13*G38*1303.1</f>
-        <v>249.61264476480684</v>
-      </c>
-      <c r="K40" s="26"/>
-    </row>
-    <row r="41" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="22">
-        <f>0.13*G38*889.81</f>
-        <v>170.44572744852491</v>
-      </c>
-      <c r="K41" s="26"/>
-    </row>
-    <row r="42" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
       <c r="J42" s="22">
-        <f>0.13*G38*36.4</f>
-        <v>6.9725272576463588</v>
-      </c>
-      <c r="K42" s="26"/>
+        <f>G42*I42</f>
+        <v>22075.47134799336</v>
+      </c>
+      <c r="K42" s="20"/>
     </row>
     <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="24"/>
-      <c r="B43" s="25"/>
+      <c r="B43" s="25" t="s">
+        <v>55</v>
+      </c>
       <c r="C43" s="26"/>
       <c r="D43" s="27"/>
       <c r="E43" s="27"/>
@@ -5698,156 +5974,1106 @@
       <c r="G43" s="27"/>
       <c r="H43" s="26"/>
       <c r="I43" s="26"/>
-      <c r="J43" s="22"/>
+      <c r="J43" s="22">
+        <f>0.13*G42*8481.2</f>
+        <v>1641.4936036638496</v>
+      </c>
       <c r="K43" s="26"/>
     </row>
-    <row r="44" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17">
-        <v>15</v>
-      </c>
-      <c r="B44" s="30" t="s">
+    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="22">
+        <f>0.13*G42*1303.1</f>
+        <v>252.20845103692426</v>
+      </c>
+      <c r="K44" s="26"/>
+    </row>
+    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="26"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="22">
+        <f>0.13*G42*889.81</f>
+        <v>172.21825018583806</v>
+      </c>
+      <c r="K45" s="26"/>
+    </row>
+    <row r="46" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="26"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="22">
+        <f>0.13*G42*36.4</f>
+        <v>7.0450369255959204</v>
+      </c>
+      <c r="K46" s="26"/>
+    </row>
+    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="26"/>
+    </row>
+    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
+        <v>5</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="13"/>
+      <c r="B49" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="15">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <f>19.17/3.281</f>
+        <v>5.8427308747333129</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="3">
+        <f>F31</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" ref="G49:G50" si="5">PRODUCT(C49:F49)</f>
+        <v>18.252969053951983</v>
+      </c>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="13"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="15">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3">
+        <f>19.17/3.281</f>
+        <v>5.8427308747333129</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="3">
+        <f>F49-2.5/3.281</f>
+        <v>2.3620847302651629</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="5"/>
+        <v>13.801025382256377</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="3">
+        <v>2</v>
+      </c>
+      <c r="D51" s="3">
+        <f>(48.5)/3.281</f>
+        <v>14.782078634562632</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G51" s="3">
+        <f>PRODUCT(C51:F51)</f>
+        <v>31.537503944510334</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="13"/>
+      <c r="B52" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="3">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3">
+        <f>(48.5-0.75*2)/3.281</f>
+        <v>14.324900944833891</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G52" s="3">
+        <f>PRODUCT(C52:F52)</f>
+        <v>30.562117224577026</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="13"/>
+      <c r="B53" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="3">
+        <f>C40</f>
+        <v>4</v>
+      </c>
+      <c r="D53" s="3">
+        <f>D40</f>
+        <v>3.2246266382200548</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3">
+        <f>F40</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G53" s="3">
+        <f>PRODUCT(C53:F53)</f>
+        <v>13.759455329192551</v>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+    </row>
+    <row r="54" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17"/>
+      <c r="B54" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="2">
+        <f>SUM(G49:G53)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J54" s="22">
+        <f>G54*I54</f>
+        <v>44837.880973279869</v>
+      </c>
+      <c r="K54" s="20"/>
+    </row>
+    <row r="55" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="24"/>
+      <c r="B55" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="22">
+        <f>0.13*G54*7010.67/100</f>
+        <v>983.50580771077557</v>
+      </c>
+      <c r="K55" s="26"/>
+    </row>
+    <row r="56" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="24"/>
+      <c r="B56" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="22">
+        <f>0.13*G54*4639.73/100</f>
+        <v>650.89376638893521</v>
+      </c>
+      <c r="K56" s="26"/>
+    </row>
+    <row r="57" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="24"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="26"/>
+    </row>
+    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="13">
+        <v>6</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="13"/>
+      <c r="B59" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3">
+        <f>G54</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3">
+        <f>PRODUCT(C59:F59)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+    </row>
+    <row r="60" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="17"/>
+      <c r="B60" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="2">
+        <f>SUM(G59:G59)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H60" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I60" s="2">
+        <v>253.8</v>
+      </c>
+      <c r="J60" s="22">
+        <f>G60*I60</f>
+        <v>27388.337403173122</v>
+      </c>
+      <c r="K60" s="20"/>
+    </row>
+    <row r="61" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="24"/>
+      <c r="B61" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="26"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="22">
+        <f>0.13*G60*2304/100</f>
+        <v>323.22123006297926</v>
+      </c>
+      <c r="K61" s="26"/>
+    </row>
+    <row r="62" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="24"/>
+      <c r="B62" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="26"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="22">
+        <f>0.13*G60*10432/100</f>
+        <v>1463.473902785156</v>
+      </c>
+      <c r="K62" s="26"/>
+    </row>
+    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="24"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="26"/>
+    </row>
+    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="13">
+        <v>7</v>
+      </c>
+      <c r="B64" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="F64" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+    </row>
+    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="13"/>
+      <c r="B65" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" s="3">
+        <v>30</v>
+      </c>
+      <c r="D65" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E65" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="F65" s="3">
+        <f>PRODUCT(C65:E65)</f>
+        <v>94.5</v>
+      </c>
+      <c r="G65" s="3">
+        <f>F65</f>
+        <v>94.5</v>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="13"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="3">
+        <v>33</v>
+      </c>
+      <c r="D66" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="F66" s="3">
+        <f>PRODUCT(C66:E66)</f>
+        <v>103.95</v>
+      </c>
+      <c r="G66" s="3">
+        <f>F66</f>
+        <v>103.95</v>
+      </c>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="13"/>
+      <c r="B67" s="63" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D67" s="3">
+        <f>28.75/3.281</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E67" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F67" s="3">
+        <f t="shared" ref="F67:F71" si="6">PRODUCT(C67:E67)</f>
+        <v>203.29167936604691</v>
+      </c>
+      <c r="G67" s="3">
+        <f t="shared" ref="G67:G72" si="7">F67</f>
+        <v>203.29167936604691</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="13"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="3">
+        <f>2*2+2</f>
+        <v>6</v>
+      </c>
+      <c r="D68" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E68" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F68" s="3">
+        <f t="shared" si="6"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="G68" s="3">
+        <f t="shared" si="7"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="13"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="3">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E69" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F69" s="3">
+        <f t="shared" ref="F69" si="8">PRODUCT(C69:E69)</f>
+        <v>95.458701615361164</v>
+      </c>
+      <c r="G69" s="3">
+        <f t="shared" si="7"/>
+        <v>95.458701615361164</v>
+      </c>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="13"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D70" s="3">
+        <f>32.25/3.281</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E70" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F70" s="3">
+        <f t="shared" si="6"/>
+        <v>228.04023163669612</v>
+      </c>
+      <c r="G70" s="3">
+        <f t="shared" si="7"/>
+        <v>228.04023163669612</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="13"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="3">
+        <f>2*2+2</f>
+        <v>6</v>
+      </c>
+      <c r="D71" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E71" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F71" s="3">
+        <f t="shared" si="6"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="7"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="13"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="3">
+        <v>9</v>
+      </c>
+      <c r="D72" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F72" s="3">
+        <f t="shared" ref="F72" si="9">PRODUCT(C72:E72)</f>
+        <v>107.3910393172813</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" si="7"/>
+        <v>107.3910393172813</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+    </row>
+    <row r="73" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="17"/>
+      <c r="B73" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="2">
+        <f>SUM(G65:G72)</f>
+        <v>975.8197043584272</v>
+      </c>
+      <c r="H73" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I73" s="2">
+        <v>182.51</v>
+      </c>
+      <c r="J73" s="22">
+        <f>G73*I73</f>
+        <v>178096.85424245655</v>
+      </c>
+      <c r="K73" s="20"/>
+    </row>
+    <row r="74" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="24"/>
+      <c r="B74" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C74" s="38"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="21">
+        <f>0.13*G73*1761.42/18.94</f>
+        <v>11797.660225693386</v>
+      </c>
+      <c r="K74" s="38"/>
+    </row>
+    <row r="75" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="24"/>
+      <c r="B75" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="26"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="22">
+        <f>0.13*G73*110/18.94</f>
+        <v>736.75933328012195</v>
+      </c>
+      <c r="K75" s="26"/>
+    </row>
+    <row r="76" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="24"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="26"/>
+    </row>
+    <row r="77" spans="1:11" ht="154.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="13">
+        <v>8</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="13"/>
+      <c r="B78" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3">
+        <f>(48.5+5+5)/3.281</f>
+        <v>17.829929899420907</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G78" s="3">
+        <f>PRODUCT(C78:F78)</f>
+        <v>26.744894849131363</v>
+      </c>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="13"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="3">
+        <v>1</v>
+      </c>
+      <c r="D79" s="3">
+        <f>(21.5+5)/3.281</f>
+        <v>8.076805851874429</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G79" s="3">
+        <f>PRODUCT(C79:F79)</f>
+        <v>12.115208777811644</v>
+      </c>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
+    </row>
+    <row r="80" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="17"/>
+      <c r="B80" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="19"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="2">
+        <f>SUM(G78:G79)</f>
+        <v>38.860103626943008</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I80" s="2">
+        <f>30571.1/10</f>
+        <v>3057.1099999999997</v>
+      </c>
+      <c r="J80" s="22">
+        <f>G80*I80</f>
+        <v>118799.61139896372</v>
+      </c>
+      <c r="K80" s="20"/>
+    </row>
+    <row r="81" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="24"/>
+      <c r="B81" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" s="26"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="22">
+        <f>0.13*G80*3302.43/10</f>
+        <v>1668.3260362694302</v>
+      </c>
+      <c r="K81" s="26"/>
+    </row>
+    <row r="82" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A82" s="24"/>
+      <c r="B82" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="26"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="22">
+        <f>0.13*G80*2981.58/10</f>
+        <v>1506.2386010362693</v>
+      </c>
+      <c r="K82" s="26"/>
+    </row>
+    <row r="83" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="24"/>
+      <c r="B83" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C83" s="26"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="22">
+        <f>0.13*G80*2273.04/10</f>
+        <v>1148.2974093264249</v>
+      </c>
+      <c r="K83" s="26"/>
+    </row>
+    <row r="84" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="24"/>
+      <c r="B84" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C84" s="26"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="22">
+        <f>0.13*G80*6383.04/10</f>
+        <v>3224.59274611399</v>
+      </c>
+      <c r="K84" s="26"/>
+    </row>
+    <row r="85" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="24"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="22"/>
+      <c r="K85" s="26"/>
+    </row>
+    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="17">
+        <v>9</v>
+      </c>
+      <c r="B86" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="C86" s="19">
+        <v>1</v>
+      </c>
+      <c r="D86" s="1"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="21">
+        <f t="shared" ref="G86" si="10">PRODUCT(C86:F86)</f>
+        <v>1</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J86" s="21">
+        <f>G86*I86</f>
+        <v>5000</v>
+      </c>
+      <c r="K86" s="20"/>
+    </row>
+    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="24"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="22"/>
+      <c r="K87" s="26"/>
+    </row>
+    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="17">
+        <v>10</v>
+      </c>
+      <c r="B88" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C88" s="19">
         <v>1</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21">
-        <f t="shared" ref="G44" si="4">PRODUCT(C44:F44)</f>
+      <c r="D88" s="1"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="21">
+        <f t="shared" ref="G88" si="11">PRODUCT(C88:F88)</f>
         <v>1</v>
       </c>
-      <c r="H44" s="21" t="s">
+      <c r="H88" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I88" s="2">
         <v>500</v>
       </c>
-      <c r="J44" s="21">
-        <f>G44*I44</f>
+      <c r="J88" s="21">
+        <f>G88*I88</f>
         <v>500</v>
       </c>
-      <c r="K44" s="20"/>
-    </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="20"/>
-    </row>
-    <row r="46" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="32"/>
-      <c r="B46" s="33" t="s">
+      <c r="K88" s="20"/>
+    </row>
+    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="17"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="22"/>
+      <c r="K89" s="20"/>
+    </row>
+    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="61"/>
+      <c r="B90" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22">
-        <f>SUM(J9:J44)</f>
-        <v>675988.13799797196</v>
-      </c>
-      <c r="K46" s="36"/>
-    </row>
-    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
-      <c r="B48" s="38" t="s">
+      <c r="C90" s="34"/>
+      <c r="D90" s="35"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="22"/>
+      <c r="I90" s="22"/>
+      <c r="J90" s="22">
+        <f>SUM(J9:J88)</f>
+        <v>1386032.0527122186</v>
+      </c>
+      <c r="K90" s="36"/>
+    </row>
+    <row r="91" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="44"/>
+    </row>
+    <row r="92" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="37"/>
+      <c r="B92" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="47">
-        <f>J46</f>
-        <v>675988.13799797196</v>
-      </c>
-      <c r="D48" s="48"/>
-      <c r="E48" s="39">
+      <c r="C92" s="53">
+        <f>J90</f>
+        <v>1386032.0527122186</v>
+      </c>
+      <c r="D92" s="54"/>
+      <c r="E92" s="39">
         <v>100</v>
       </c>
-      <c r="F48" s="37"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="42"/>
-      <c r="K48" s="43"/>
-    </row>
-    <row r="49" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="38" t="s">
+      <c r="F92" s="37"/>
+      <c r="G92" s="40"/>
+      <c r="H92" s="37"/>
+      <c r="I92" s="41"/>
+      <c r="J92" s="42"/>
+      <c r="K92" s="43"/>
+    </row>
+    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="44"/>
+      <c r="B93" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="49">
-        <v>700000</v>
-      </c>
-      <c r="D49" s="50"/>
-      <c r="E49" s="39"/>
-    </row>
-    <row r="50" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="38" t="s">
+      <c r="C93" s="57">
+        <v>1200000</v>
+      </c>
+      <c r="D93" s="58"/>
+      <c r="E93" s="39"/>
+    </row>
+    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="44"/>
+      <c r="B94" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="49">
-        <f>C49-C52-C53</f>
-        <v>665000</v>
-      </c>
-      <c r="D50" s="50"/>
-      <c r="E50" s="39">
-        <f>C50/C48*100</f>
-        <v>98.374507276042621</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="38" t="s">
+      <c r="C94" s="57">
+        <f>C93-C96-C97</f>
+        <v>1140000</v>
+      </c>
+      <c r="D94" s="58"/>
+      <c r="E94" s="39">
+        <f>C94/C92*100</f>
+        <v>82.249180152019036</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="44"/>
+      <c r="B95" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="51">
-        <f>C48-C50</f>
-        <v>10988.137997971964</v>
-      </c>
-      <c r="D51" s="51"/>
-      <c r="E51" s="39">
-        <f>100-E50</f>
-        <v>1.6254927239573789</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="38" t="s">
+      <c r="C95" s="59">
+        <f>C92-C94</f>
+        <v>246032.0527122186</v>
+      </c>
+      <c r="D95" s="59"/>
+      <c r="E95" s="39">
+        <f>100-E94</f>
+        <v>17.750819847980964</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="44"/>
+      <c r="B96" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="47">
-        <f>C49*0.03</f>
-        <v>21000</v>
-      </c>
-      <c r="D52" s="48"/>
-      <c r="E52" s="39">
+      <c r="C96" s="53">
+        <f>C93*0.03</f>
+        <v>36000</v>
+      </c>
+      <c r="D96" s="54"/>
+      <c r="E96" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="38" t="s">
+    <row r="97" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="44"/>
+      <c r="B97" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="47">
-        <f>C49*0.02</f>
-        <v>14000</v>
-      </c>
-      <c r="D53" s="48"/>
-      <c r="E53" s="39">
+      <c r="C97" s="53">
+        <f>C93*0.02</f>
+        <v>24000</v>
+      </c>
+      <c r="D97" s="54"/>
+      <c r="E97" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -5855,14 +7081,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>

--- a/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
+++ b/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5618C2-409A-4CC4-B70D-27F9F5D3E684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
@@ -34,11 +33,11 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$158</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$101</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">krishi!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="126">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -650,14 +649,17 @@
       <t xml:space="preserve"> s[lif pkh ;+sng s]Gb| lgdf{0f</t>
     </r>
   </si>
+  <si>
+    <t>l;d]G6 jf jh|df hf]8]sf] uf/f] eTsfO{ To;af6 cfPsf] ;fdfu+|L !) dL</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -828,9 +830,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -846,14 +848,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -882,7 +884,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -919,7 +921,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -937,7 +939,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -946,46 +948,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1008,14 +973,51 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1031,7 +1033,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1125,7 +1127,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1184,7 +1186,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1248,9 +1250,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1288,9 +1290,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1325,7 +1327,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1360,7 +1362,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1533,7 +1535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M158"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1549,113 +1551,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4958,11 +4960,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="53">
+      <c r="C153" s="54">
         <f>J151</f>
         <v>520268.58119831659</v>
       </c>
-      <c r="D153" s="54"/>
+      <c r="D153" s="55"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4977,21 +4979,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="57">
+      <c r="C154" s="56">
         <v>700000</v>
       </c>
-      <c r="D154" s="58"/>
+      <c r="D154" s="57"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="57">
+      <c r="C155" s="56">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="58"/>
+      <c r="D155" s="57"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>127.81859678482381</v>
@@ -5001,11 +5003,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="59">
+      <c r="C156" s="58">
         <f>C153-C155</f>
         <v>-144731.41880168341</v>
       </c>
-      <c r="D156" s="59"/>
+      <c r="D156" s="58"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>-27.818596784823811</v>
@@ -5015,11 +5017,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="53">
+      <c r="C157" s="54">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="54"/>
+      <c r="D157" s="55"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -5028,23 +5030,17 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="53">
+      <c r="C158" s="54">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="54"/>
+      <c r="D158" s="55"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -5054,6 +5050,12 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -5064,8 +5066,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K97"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="14" customWidth="1"/>
@@ -5080,116 +5082,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="47" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -6388,16 +6390,16 @@
       <c r="B64" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C64" s="62" t="s">
+      <c r="C64" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="62" t="s">
+      <c r="D64" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E64" s="62" t="s">
+      <c r="E64" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="F64" s="62" t="s">
+      <c r="F64" s="49" t="s">
         <v>107</v>
       </c>
       <c r="G64" s="15"/>
@@ -6408,7 +6410,7 @@
     </row>
     <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="13"/>
-      <c r="B65" s="63" t="s">
+      <c r="B65" s="50" t="s">
         <v>109</v>
       </c>
       <c r="C65" s="3">
@@ -6458,9 +6460,9 @@
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="13"/>
-      <c r="B67" s="63" t="s">
+      <c r="B67" s="50" t="s">
         <v>110</v>
       </c>
       <c r="C67" s="3">
@@ -6647,7 +6649,7 @@
     </row>
     <row r="74" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="24"/>
-      <c r="B74" s="65" t="s">
+      <c r="B74" s="52" t="s">
         <v>112</v>
       </c>
       <c r="C74" s="38"/>
@@ -6694,7 +6696,7 @@
       <c r="J76" s="22"/>
       <c r="K76" s="26"/>
     </row>
-    <row r="77" spans="1:11" ht="154.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="138.75" x14ac:dyDescent="0.25">
       <c r="A77" s="13">
         <v>8</v>
       </c>
@@ -6805,7 +6807,7 @@
     </row>
     <row r="82" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="24"/>
-      <c r="B82" s="64" t="s">
+      <c r="B82" s="51" t="s">
         <v>118</v>
       </c>
       <c r="C82" s="26"/>
@@ -6823,7 +6825,7 @@
     </row>
     <row r="83" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="24"/>
-      <c r="B83" s="64" t="s">
+      <c r="B83" s="51" t="s">
         <v>119</v>
       </c>
       <c r="C83" s="26"/>
@@ -6870,210 +6872,285 @@
       <c r="J85" s="22"/>
       <c r="K85" s="26"/>
     </row>
-    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="17">
         <v>9</v>
       </c>
-      <c r="B86" s="66" t="s">
-        <v>123</v>
-      </c>
-      <c r="C86" s="19">
-        <v>1</v>
-      </c>
+      <c r="B86" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C86" s="19"/>
       <c r="D86" s="1"/>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
-      <c r="G86" s="21">
-        <f t="shared" ref="G86" si="10">PRODUCT(C86:F86)</f>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="20"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="13"/>
+      <c r="B87" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C87" s="3">
         <v>1</v>
       </c>
-      <c r="H86" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J86" s="21">
-        <f>G86*I86</f>
-        <v>5000</v>
-      </c>
-      <c r="K86" s="20"/>
-    </row>
-    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="27"/>
-      <c r="E87" s="27"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="26"/>
-      <c r="I87" s="26"/>
-      <c r="J87" s="22"/>
-      <c r="K87" s="26"/>
+      <c r="D87" s="3">
+        <f>D31</f>
+        <v>5.6141420298689431</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F87" s="3">
+        <f>7.5/3.281</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G87" s="3">
+        <f>PRODUCT(C87:F87)</f>
+        <v>1.2833302415122547</v>
+      </c>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
     </row>
     <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="17">
-        <v>10</v>
-      </c>
-      <c r="B88" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" s="19">
-        <v>1</v>
-      </c>
+      <c r="A88" s="17"/>
+      <c r="B88" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" s="19"/>
       <c r="D88" s="1"/>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
-      <c r="G88" s="21">
-        <f t="shared" ref="G88" si="11">PRODUCT(C88:F88)</f>
+      <c r="G88" s="2">
+        <f>SUM(G86:G87)</f>
+        <v>1.2833302415122547</v>
+      </c>
+      <c r="H88" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="2">
+        <v>1982.2</v>
+      </c>
+      <c r="J88" s="22">
+        <f>G88*I88</f>
+        <v>2543.8172047255912</v>
+      </c>
+      <c r="K88" s="20"/>
+    </row>
+    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="24"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="27"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="22"/>
+      <c r="K89" s="26"/>
+    </row>
+    <row r="90" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="17">
+        <v>10</v>
+      </c>
+      <c r="B90" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C90" s="19">
         <v>1</v>
       </c>
-      <c r="H88" s="21" t="s">
+      <c r="D90" s="1"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="21">
+        <f t="shared" ref="G90" si="10">PRODUCT(C90:F90)</f>
+        <v>1</v>
+      </c>
+      <c r="H90" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J90" s="21">
+        <f>G90*I90</f>
+        <v>5000</v>
+      </c>
+      <c r="K90" s="20"/>
+    </row>
+    <row r="91" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="24"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="27"/>
+      <c r="H91" s="26"/>
+      <c r="I91" s="26"/>
+      <c r="J91" s="22"/>
+      <c r="K91" s="26"/>
+    </row>
+    <row r="92" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="17">
+        <v>11</v>
+      </c>
+      <c r="B92" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="19">
+        <v>1</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="21">
+        <f t="shared" ref="G92" si="11">PRODUCT(C92:F92)</f>
+        <v>1</v>
+      </c>
+      <c r="H92" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I88" s="2">
+      <c r="I92" s="2">
         <v>500</v>
       </c>
-      <c r="J88" s="21">
-        <f>G88*I88</f>
+      <c r="J92" s="21">
+        <f>G92*I92</f>
         <v>500</v>
       </c>
-      <c r="K88" s="20"/>
-    </row>
-    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="21"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="22"/>
-      <c r="K89" s="20"/>
-    </row>
-    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="61"/>
-      <c r="B90" s="33" t="s">
+      <c r="K92" s="20"/>
+    </row>
+    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="17"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="21"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="22"/>
+      <c r="K93" s="20"/>
+    </row>
+    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="48"/>
+      <c r="B94" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C90" s="34"/>
-      <c r="D90" s="35"/>
-      <c r="E90" s="35"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="22"/>
-      <c r="H90" s="22"/>
-      <c r="I90" s="22"/>
-      <c r="J90" s="22">
-        <f>SUM(J9:J88)</f>
-        <v>1386032.0527122186</v>
-      </c>
-      <c r="K90" s="36"/>
-    </row>
-    <row r="91" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="44"/>
-    </row>
-    <row r="92" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="37"/>
-      <c r="B92" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C92" s="53">
-        <f>J90</f>
-        <v>1386032.0527122186</v>
-      </c>
-      <c r="D92" s="54"/>
-      <c r="E92" s="39">
-        <v>100</v>
-      </c>
-      <c r="F92" s="37"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="41"/>
-      <c r="J92" s="42"/>
-      <c r="K92" s="43"/>
-    </row>
-    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="44"/>
-      <c r="B93" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C93" s="57">
-        <v>1200000</v>
-      </c>
-      <c r="D93" s="58"/>
-      <c r="E93" s="39"/>
-    </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="44"/>
-      <c r="B94" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C94" s="57">
-        <f>C93-C96-C97</f>
-        <v>1140000</v>
-      </c>
-      <c r="D94" s="58"/>
-      <c r="E94" s="39">
-        <f>C94/C92*100</f>
-        <v>82.249180152019036</v>
-      </c>
+      <c r="C94" s="34"/>
+      <c r="D94" s="35"/>
+      <c r="E94" s="35"/>
+      <c r="F94" s="35"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="22"/>
+      <c r="J94" s="22">
+        <f>SUM(J9:J92)</f>
+        <v>1388575.8699169443</v>
+      </c>
+      <c r="K94" s="36"/>
     </row>
     <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="44"/>
-      <c r="B95" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C95" s="59">
-        <f>C92-C94</f>
-        <v>246032.0527122186</v>
-      </c>
-      <c r="D95" s="59"/>
-      <c r="E95" s="39">
-        <f>100-E94</f>
-        <v>17.750819847980964</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="44"/>
+    </row>
+    <row r="96" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="37"/>
       <c r="B96" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96" s="53">
-        <f>C93*0.03</f>
-        <v>36000</v>
-      </c>
-      <c r="D96" s="54"/>
+        <v>19</v>
+      </c>
+      <c r="C96" s="54">
+        <f>J94</f>
+        <v>1388575.8699169443</v>
+      </c>
+      <c r="D96" s="55"/>
       <c r="E96" s="39">
-        <v>3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F96" s="37"/>
+      <c r="G96" s="40"/>
+      <c r="H96" s="37"/>
+      <c r="I96" s="41"/>
+      <c r="J96" s="42"/>
+      <c r="K96" s="43"/>
     </row>
     <row r="97" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="44"/>
       <c r="B97" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="56">
+        <v>1200000</v>
+      </c>
+      <c r="D97" s="57"/>
+      <c r="E97" s="39"/>
+    </row>
+    <row r="98" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="44"/>
+      <c r="B98" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C98" s="56">
+        <f>C97-C100-C101</f>
+        <v>1140000</v>
+      </c>
+      <c r="D98" s="57"/>
+      <c r="E98" s="39">
+        <f>C98/C96*100</f>
+        <v>82.098502840049164</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="44"/>
+      <c r="B99" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" s="58">
+        <f>C96-C98</f>
+        <v>248575.8699169443</v>
+      </c>
+      <c r="D99" s="58"/>
+      <c r="E99" s="39">
+        <f>100-E98</f>
+        <v>17.901497159950836</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="44"/>
+      <c r="B100" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" s="54">
+        <f>C97*0.03</f>
+        <v>36000</v>
+      </c>
+      <c r="D100" s="55"/>
+      <c r="E100" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="44"/>
+      <c r="B101" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C97" s="53">
-        <f>C93*0.02</f>
+      <c r="C101" s="54">
+        <f>C97*0.02</f>
         <v>24000</v>
       </c>
-      <c r="D97" s="54"/>
-      <c r="E97" s="39">
+      <c r="D101" s="55"/>
+      <c r="E101" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -7081,6 +7158,14 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>

--- a/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
+++ b/बजेट माग estimate/thekka/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१/कृषि उपज संकलन केन्द्र निर्माण - शंखरापुर -१.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6666918C-922B-4112-BDD9-C01521AEFFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
     <sheet name="krishi" sheetId="14" r:id="rId2"/>
+    <sheet name="krishi thekka" sheetId="15" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
@@ -33,11 +35,13 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$158</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">krishi!$A$1:$K$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'krishi thekka'!$A$1:$K$77</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">krishi!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'krishi thekka'!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="130">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -652,14 +656,26 @@
   <si>
     <t>l;d]G6 jf jh|df hf]8]sf] uf/f] eTsfO{ To;af6 cfPsf] ;fdfu+|L !) dL</t>
   </si>
+  <si>
+    <t>-office room</t>
+  </si>
+  <si>
+    <t>-deduction for door area</t>
+  </si>
+  <si>
+    <t>VAT 13%</t>
+  </si>
+  <si>
+    <t>Grand total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -830,13 +846,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -848,14 +864,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -884,7 +900,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -921,7 +937,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -939,7 +955,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -948,8 +964,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -973,23 +989,10 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1004,20 +1007,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1033,7 +1052,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1127,7 +1146,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1186,7 +1205,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1250,9 +1269,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1290,9 +1309,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1327,7 +1346,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1362,7 +1381,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1535,7 +1554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M158"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1551,113 +1570,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="60" t="s">
+      <c r="H7" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4960,11 +4979,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="54">
+      <c r="C153" s="60">
         <f>J151</f>
         <v>520268.58119831659</v>
       </c>
-      <c r="D153" s="55"/>
+      <c r="D153" s="61"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4979,21 +4998,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="56">
+      <c r="C154" s="64">
         <v>700000</v>
       </c>
-      <c r="D154" s="57"/>
+      <c r="D154" s="65"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="56">
+      <c r="C155" s="64">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="57"/>
+      <c r="D155" s="65"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>127.81859678482381</v>
@@ -5003,11 +5022,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="58">
+      <c r="C156" s="66">
         <f>C153-C155</f>
         <v>-144731.41880168341</v>
       </c>
-      <c r="D156" s="58"/>
+      <c r="D156" s="66"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>-27.818596784823811</v>
@@ -5017,11 +5036,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="54">
+      <c r="C157" s="60">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="55"/>
+      <c r="D157" s="61"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -5030,17 +5049,23 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="54">
+      <c r="C158" s="60">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="55"/>
+      <c r="D158" s="61"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -5050,12 +5075,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -5066,8 +5085,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="14" customWidth="1"/>
@@ -5082,113 +5101,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="60" t="s">
+      <c r="H7" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
@@ -5284,7 +5303,7 @@
         <v>0.75</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" ref="G11:G13" si="0">PRODUCT(C11:F11)</f>
+        <f t="shared" ref="G11:G15" si="0">PRODUCT(C11:F11)</f>
         <v>8.9911612313319118</v>
       </c>
       <c r="H11" s="15"/>
@@ -5342,66 +5361,2263 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="15">
+        <v>-2</v>
+      </c>
+      <c r="D14" s="3">
+        <f>42/12/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>-1.600121914050594</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="3">
+        <f>35/12/3.281</f>
+        <v>0.88895661891699673</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.66671746418774758</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="2">
-        <f>SUM(G10:G13)</f>
-        <v>67.965643349752952</v>
-      </c>
-      <c r="H14" s="21" t="s">
+      <c r="C16" s="19"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="2">
+        <f>SUM(G10:G15)</f>
+        <v>65.698803971514621</v>
+      </c>
+      <c r="H16" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I16" s="2">
         <v>9949.51</v>
       </c>
-      <c r="J14" s="22">
-        <f>G14*I14</f>
-        <v>676224.84816480055</v>
-      </c>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25" t="s">
+      <c r="J16" s="22">
+        <f>G16*I16</f>
+        <v>653670.90710262442</v>
+      </c>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="22">
-        <f>0.13*G14*90530.95/10</f>
-        <v>79988.925377586129</v>
-      </c>
-      <c r="K15" s="26"/>
-    </row>
-    <row r="16" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25" t="s">
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="22">
+        <f>0.13*G16*90530.95/10</f>
+        <v>77321.076786264879</v>
+      </c>
+      <c r="K17" s="26"/>
+    </row>
+    <row r="18" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="22">
+        <f>0.13*G16*264/10</f>
+        <v>225.47829523023816</v>
+      </c>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>2</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <f>35.083/3.281</f>
+        <v>10.692776592502286</v>
+      </c>
+      <c r="E21" s="3">
+        <f>236/12/3.281</f>
+        <v>5.9941074875546079</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3">
+        <f>PRODUCT(C21:F21)</f>
+        <v>64.0936522358666</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="15">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="3">
+        <f>D12</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E22" s="3">
+        <f>E12</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3">
+        <f t="shared" ref="G22:G24" si="1">PRODUCT(C22:F22)</f>
+        <v>-18.027236698767414</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="15">
+        <v>-1</v>
+      </c>
+      <c r="D23" s="3">
+        <f>D13</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E23" s="3">
+        <f>E13</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3">
+        <f t="shared" si="1"/>
+        <v>-20.221856818617361</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="15">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <f>10.667/3.281</f>
+        <v>3.2511429442243216</v>
+      </c>
+      <c r="E24" s="3">
+        <f>236/12/3.281</f>
+        <v>5.9941074875546079</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3">
+        <f t="shared" si="1"/>
+        <v>19.487700265085341</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+    </row>
+    <row r="25" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="2">
+        <f>SUM(G21:G24)</f>
+        <v>45.332258983567172</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="2">
+        <v>2808.56</v>
+      </c>
+      <c r="J25" s="22">
+        <f>G25*I25</f>
+        <v>127318.36929088741</v>
+      </c>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="22">
+        <f>0.13*G25*24855.6/10</f>
+        <v>14647.886453095378</v>
+      </c>
+      <c r="K26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="22">
+        <f>0.13*G25*50/10</f>
+        <v>29.465968339318664</v>
+      </c>
+      <c r="K27" s="26"/>
+    </row>
+    <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="22">
+        <f>0.13*G25*300/10</f>
+        <v>176.79581003591198</v>
+      </c>
+      <c r="K28" s="26"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>3</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3">
+        <f>(48.5/3.281)</f>
+        <v>14.782078634562632</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" ref="F31:F33" si="2">2.75/3.281</f>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G31" s="3">
+        <f>PRODUCT(C31:F31)</f>
+        <v>5.6992774985436547</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="3">
+        <f>-5*2</f>
+        <v>-10</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" ref="G32" si="3">PRODUCT(C32:F32)</f>
+        <v>-0.67471807375800064</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
+      <c r="B33" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="3">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" ref="G33" si="4">PRODUCT(C33:F33)</f>
+        <v>1.0267448948491313</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3">
+        <f>((19.17-0.75)/3.281)</f>
+        <v>5.6141420298689431</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F34" s="3">
+        <f>(7.5+2.75)/3.281</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G34" s="3">
+        <f>PRODUCT(C34:F34)</f>
+        <v>1.7538846634000815</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F35" s="3">
+        <f>(7.5+2.75)/3.281</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G35" s="3">
+        <f>PRODUCT(C35:F35)</f>
+        <v>0.16526211520877782</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="2">
+        <f>SUM(G31:G35)</f>
+        <v>7.9704510982436449</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="2">
+        <f>14491.84</f>
+        <v>14491.84</v>
+      </c>
+      <c r="J36" s="22">
+        <f>G36*I36</f>
+        <v>115506.50204357118</v>
+      </c>
+      <c r="K36" s="20"/>
+    </row>
+    <row r="37" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="22">
+        <f>0.13*G36*8481.2</f>
+        <v>8787.8686810751205</v>
+      </c>
+      <c r="K37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="22">
+        <f>0.13*G36*912.17</f>
+        <v>945.15282917703769</v>
+      </c>
+      <c r="K38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="26"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="22">
+        <f>0.13*G36*953.37</f>
+        <v>987.8425652592307</v>
+      </c>
+      <c r="K39" s="26"/>
+    </row>
+    <row r="40" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="22">
+        <f>0.13*G36*28</f>
+        <v>29.012441997606867</v>
+      </c>
+      <c r="K40" s="26"/>
+    </row>
+    <row r="41" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="26"/>
+    </row>
+    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="13">
+        <v>4</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D43" s="3">
+        <f>(11.33-0.75)/3.281</f>
+        <v>3.2246266382200548</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F43" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G43" s="3">
+        <f>PRODUCT(C43:F43)</f>
+        <v>1.3759455329192551</v>
+      </c>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="13"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F44" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G44" s="3">
+        <f>PRODUCT(C44:F44)</f>
+        <v>0.11286193233770191</v>
+      </c>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+    </row>
+    <row r="45" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="2">
+        <f>SUM(G43:G44)</f>
+        <v>1.488807465256957</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="2">
+        <v>14827.62</v>
+      </c>
+      <c r="J45" s="22">
+        <f>G45*I45</f>
+        <v>22075.47134799336</v>
+      </c>
+      <c r="K45" s="20"/>
+    </row>
+    <row r="46" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="26"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="22">
+        <f>0.13*G45*8481.2</f>
+        <v>1641.4936036638496</v>
+      </c>
+      <c r="K46" s="26"/>
+    </row>
+    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="26"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="22">
+        <f>0.13*G45*1303.1</f>
+        <v>252.20845103692426</v>
+      </c>
+      <c r="K47" s="26"/>
+    </row>
+    <row r="48" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="26"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="22">
+        <f>0.13*G45*889.81</f>
+        <v>172.21825018583806</v>
+      </c>
+      <c r="K48" s="26"/>
+    </row>
+    <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24"/>
+      <c r="B49" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="26"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="22">
+        <f>0.13*G45*36.4</f>
+        <v>7.0450369255959204</v>
+      </c>
+      <c r="K49" s="26"/>
+    </row>
+    <row r="50" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="26"/>
+    </row>
+    <row r="51" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="13">
+        <v>5</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="13"/>
+      <c r="B52" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="15">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3">
+        <f>19.17/3.281</f>
+        <v>5.8427308747333129</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="3">
+        <f>F34</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" ref="G52:G53" si="5">PRODUCT(C52:F52)</f>
+        <v>18.252969053951983</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="13"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="15">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3">
+        <f>19.17/3.281</f>
+        <v>5.8427308747333129</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="3">
+        <f>F52-2.5/3.281</f>
+        <v>2.3620847302651629</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="5"/>
+        <v>13.801025382256377</v>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
+      <c r="B54" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="3">
+        <v>2</v>
+      </c>
+      <c r="D54" s="3">
+        <f>(48.5)/3.281</f>
+        <v>14.782078634562632</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G54" s="3">
+        <f>PRODUCT(C54:F54)</f>
+        <v>31.537503944510334</v>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="13"/>
+      <c r="B55" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="3">
+        <v>2</v>
+      </c>
+      <c r="D55" s="3">
+        <f>(48.5-0.75*2)/3.281</f>
+        <v>14.324900944833891</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G55" s="3">
+        <f>PRODUCT(C55:F55)</f>
+        <v>30.562117224577026</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="13"/>
+      <c r="B56" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="3">
+        <f>C43</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="3">
+        <f>D43</f>
+        <v>3.2246266382200548</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3">
+        <f>F43</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G56" s="3">
+        <f>PRODUCT(C56:F56)</f>
+        <v>13.759455329192551</v>
+      </c>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+    </row>
+    <row r="57" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="17"/>
+      <c r="B57" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="2">
+        <f>SUM(G52:G56)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J57" s="22">
+        <f>G57*I57</f>
+        <v>44837.880973279869</v>
+      </c>
+      <c r="K57" s="20"/>
+    </row>
+    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+      <c r="B58" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="26"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="22">
+        <f>0.13*G57*7010.67/100</f>
+        <v>983.50580771077557</v>
+      </c>
+      <c r="K58" s="26"/>
+    </row>
+    <row r="59" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="24"/>
+      <c r="B59" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="26"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="22">
+        <f>0.13*G57*4639.73/100</f>
+        <v>650.89376638893521</v>
+      </c>
+      <c r="K59" s="26"/>
+    </row>
+    <row r="60" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="24"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="26"/>
+    </row>
+    <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="13">
+        <v>6</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="13"/>
+      <c r="B62" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3">
+        <f>G57</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3">
+        <f>PRODUCT(C62:F62)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+    </row>
+    <row r="63" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="17"/>
+      <c r="B63" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="2">
+        <f>SUM(G62:G62)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H63" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I63" s="2">
+        <v>253.8</v>
+      </c>
+      <c r="J63" s="22">
+        <f>G63*I63</f>
+        <v>27388.337403173122</v>
+      </c>
+      <c r="K63" s="20"/>
+    </row>
+    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="24"/>
+      <c r="B64" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="22">
+        <f>0.13*G63*2304/100</f>
+        <v>323.22123006297926</v>
+      </c>
+      <c r="K64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="24"/>
+      <c r="B65" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="26"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="22">
+        <f>0.13*G63*10432/100</f>
+        <v>1463.473902785156</v>
+      </c>
+      <c r="K65" s="26"/>
+    </row>
+    <row r="66" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="24"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="26"/>
+    </row>
+    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="13">
+        <v>7</v>
+      </c>
+      <c r="B67" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+    </row>
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="13"/>
+      <c r="B68" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="3">
+        <v>30</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E68" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="F68" s="3">
+        <f>PRODUCT(C68:E68)</f>
+        <v>94.5</v>
+      </c>
+      <c r="G68" s="3">
+        <f>F68</f>
+        <v>94.5</v>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="13"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="3">
+        <v>33</v>
+      </c>
+      <c r="D69" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E69" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="F69" s="3">
+        <f>PRODUCT(C69:E69)</f>
+        <v>103.95</v>
+      </c>
+      <c r="G69" s="3">
+        <f>F69</f>
+        <v>103.95</v>
+      </c>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+    </row>
+    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="13"/>
+      <c r="B70" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D70" s="3">
+        <f>28.75/3.281</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E70" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F70" s="3">
+        <f t="shared" ref="F70:F74" si="6">PRODUCT(C70:E70)</f>
+        <v>203.29167936604691</v>
+      </c>
+      <c r="G70" s="3">
+        <f t="shared" ref="G70:G75" si="7">F70</f>
+        <v>203.29167936604691</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="13"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="3">
+        <f>2*2+2</f>
+        <v>6</v>
+      </c>
+      <c r="D71" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E71" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F71" s="3">
+        <f t="shared" si="6"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="7"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="13"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="3">
+        <v>8</v>
+      </c>
+      <c r="D72" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F72" s="3">
+        <f t="shared" ref="F72" si="8">PRODUCT(C72:E72)</f>
+        <v>95.458701615361164</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" si="7"/>
+        <v>95.458701615361164</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="13"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D73" s="3">
+        <f>32.25/3.281</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E73" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F73" s="3">
+        <f t="shared" si="6"/>
+        <v>228.04023163669612</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" si="7"/>
+        <v>228.04023163669612</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="13"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="3">
+        <f>2*2+2</f>
+        <v>6</v>
+      </c>
+      <c r="D74" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E74" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F74" s="3">
+        <f t="shared" si="6"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" si="7"/>
+        <v>71.59402621152087</v>
+      </c>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="13"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="3">
+        <v>9</v>
+      </c>
+      <c r="D75" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E75" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" ref="F75" si="9">PRODUCT(C75:E75)</f>
+        <v>107.3910393172813</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="7"/>
+        <v>107.3910393172813</v>
+      </c>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+    </row>
+    <row r="76" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="17"/>
+      <c r="B76" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="2">
+        <f>SUM(G68:G75)</f>
+        <v>975.8197043584272</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I76" s="2">
+        <v>182.51</v>
+      </c>
+      <c r="J76" s="22">
+        <f>G76*I76</f>
+        <v>178096.85424245655</v>
+      </c>
+      <c r="K76" s="20"/>
+    </row>
+    <row r="77" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="24"/>
+      <c r="B77" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="38"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
+      <c r="J77" s="21">
+        <f>0.13*G76*1761.42/18.94</f>
+        <v>11797.660225693386</v>
+      </c>
+      <c r="K77" s="38"/>
+    </row>
+    <row r="78" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="24"/>
+      <c r="B78" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="26"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="22">
+        <f>0.13*G76*110/18.94</f>
+        <v>736.75933328012195</v>
+      </c>
+      <c r="K78" s="26"/>
+    </row>
+    <row r="79" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="24"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="26"/>
+    </row>
+    <row r="80" spans="1:11" ht="138.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="13">
+        <v>8</v>
+      </c>
+      <c r="B80" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="13"/>
+      <c r="B81" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3">
+        <f>(48.5+5+5)/3.281</f>
+        <v>17.829929899420907</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="G81" s="3">
+        <f>PRODUCT(C81:F81)</f>
+        <v>32.093873818957633</v>
+      </c>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="13"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3">
+        <f>(21.5+5)/3.281</f>
+        <v>8.076805851874429</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="G82" s="3">
+        <f>PRODUCT(C82:F82)</f>
+        <v>14.538250533373972</v>
+      </c>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+    </row>
+    <row r="83" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="17"/>
+      <c r="B83" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="19"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="2">
+        <f>SUM(G81:G82)</f>
+        <v>46.632124352331601</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I83" s="2">
+        <f>30571.1/10</f>
+        <v>3057.1099999999997</v>
+      </c>
+      <c r="J83" s="22">
+        <f>G83*I83</f>
+        <v>142559.53367875644</v>
+      </c>
+      <c r="K83" s="20"/>
+    </row>
+    <row r="84" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="24"/>
+      <c r="B84" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C84" s="26"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="22">
+        <f>0.13*G83*3302.43/10</f>
+        <v>2001.9912435233157</v>
+      </c>
+      <c r="K84" s="26"/>
+    </row>
+    <row r="85" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="24"/>
+      <c r="B85" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85" s="26"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="22">
+        <f>0.13*G83*2981.58/10</f>
+        <v>1807.486321243523</v>
+      </c>
+      <c r="K85" s="26"/>
+    </row>
+    <row r="86" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A86" s="24"/>
+      <c r="B86" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C86" s="26"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="22">
+        <f>0.13*G83*2273.04/10</f>
+        <v>1377.9568911917097</v>
+      </c>
+      <c r="K86" s="26"/>
+    </row>
+    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="24"/>
+      <c r="B87" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C87" s="26"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="22">
+        <f>0.13*G83*6383.04/10</f>
+        <v>3869.511295336787</v>
+      </c>
+      <c r="K87" s="26"/>
+    </row>
+    <row r="88" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="24"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="27"/>
+      <c r="H88" s="26"/>
+      <c r="I88" s="26"/>
+      <c r="J88" s="22"/>
+      <c r="K88" s="26"/>
+    </row>
+    <row r="89" spans="1:11" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A89" s="17">
+        <v>9</v>
+      </c>
+      <c r="B89" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C89" s="19"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="21"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="20"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="13"/>
+      <c r="B90" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3">
+        <f>D34</f>
+        <v>5.6141420298689431</v>
+      </c>
+      <c r="E90" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F90" s="3">
+        <f>7.5/3.281</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G90" s="3">
+        <f>PRODUCT(C90:F90)</f>
+        <v>1.2833302415122547</v>
+      </c>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
+    </row>
+    <row r="91" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="17"/>
+      <c r="B91" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="19"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="2">
+        <f>SUM(G89:G90)</f>
+        <v>1.2833302415122547</v>
+      </c>
+      <c r="H91" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" s="2">
+        <v>1982.2</v>
+      </c>
+      <c r="J91" s="22">
+        <f>G91*I91</f>
+        <v>2543.8172047255912</v>
+      </c>
+      <c r="K91" s="20"/>
+    </row>
+    <row r="92" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="24"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
+      <c r="G92" s="27"/>
+      <c r="H92" s="26"/>
+      <c r="I92" s="26"/>
+      <c r="J92" s="22"/>
+      <c r="K92" s="26"/>
+    </row>
+    <row r="93" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="17">
+        <v>10</v>
+      </c>
+      <c r="B93" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C93" s="19">
+        <v>1</v>
+      </c>
+      <c r="D93" s="1"/>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="21">
+        <f t="shared" ref="G93" si="10">PRODUCT(C93:F93)</f>
+        <v>1</v>
+      </c>
+      <c r="H93" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J93" s="21">
+        <f>G93*I93</f>
+        <v>5000</v>
+      </c>
+      <c r="K93" s="20"/>
+    </row>
+    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="26"/>
+      <c r="J94" s="22"/>
+      <c r="K94" s="26"/>
+    </row>
+    <row r="95" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="17">
+        <v>11</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="19">
+        <v>1</v>
+      </c>
+      <c r="D95" s="1"/>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20"/>
+      <c r="G95" s="21">
+        <f t="shared" ref="G95" si="11">PRODUCT(C95:F95)</f>
+        <v>1</v>
+      </c>
+      <c r="H95" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" s="2">
+        <v>500</v>
+      </c>
+      <c r="J95" s="21">
+        <f>G95*I95</f>
+        <v>500</v>
+      </c>
+      <c r="K95" s="20"/>
+    </row>
+    <row r="96" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="17"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="21"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="22"/>
+      <c r="K96" s="20"/>
+    </row>
+    <row r="97" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="48"/>
+      <c r="B97" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="34"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="35"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22">
+        <f>SUM(J9:J95)</f>
+        <v>1449733.6784769716</v>
+      </c>
+      <c r="K97" s="36"/>
+    </row>
+    <row r="98" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="44"/>
+    </row>
+    <row r="99" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="37"/>
+      <c r="B99" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="60">
+        <f>J97</f>
+        <v>1449733.6784769716</v>
+      </c>
+      <c r="D99" s="61"/>
+      <c r="E99" s="39">
+        <v>100</v>
+      </c>
+      <c r="F99" s="37"/>
+      <c r="G99" s="40"/>
+      <c r="H99" s="37"/>
+      <c r="I99" s="41"/>
+      <c r="J99" s="42"/>
+      <c r="K99" s="43"/>
+    </row>
+    <row r="100" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="44"/>
+      <c r="B100" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="64">
+        <v>1600000</v>
+      </c>
+      <c r="D100" s="65"/>
+      <c r="E100" s="39"/>
+    </row>
+    <row r="101" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="44"/>
+      <c r="B101" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="64">
+        <f>C100-C103-C104</f>
+        <v>1520000</v>
+      </c>
+      <c r="D101" s="65"/>
+      <c r="E101" s="39">
+        <f>C101/C99*100</f>
+        <v>104.84684342829418</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="44"/>
+      <c r="B102" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="66">
+        <f>C99-C101</f>
+        <v>-70266.321523028426</v>
+      </c>
+      <c r="D102" s="66"/>
+      <c r="E102" s="39">
+        <f>100-E101</f>
+        <v>-4.8468434282941786</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="44"/>
+      <c r="B103" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" s="60">
+        <f>C100*0.03</f>
+        <v>48000</v>
+      </c>
+      <c r="D103" s="61"/>
+      <c r="E103" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="44"/>
+      <c r="B104" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" s="60">
+        <f>C100*0.02</f>
+        <v>32000</v>
+      </c>
+      <c r="D104" s="61"/>
+      <c r="E104" s="39">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6C7C2F-1478-4A13-8446-41B228967A5A}">
+  <dimension ref="A1:K77"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+    </row>
+    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>1</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="15">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <f>(272+272)/12/3.281</f>
+        <v>13.81692573402418</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G10" s="3">
+        <f>PRODUCT(C10:F10)</f>
+        <v>20.725388601036268</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="15">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <f>236/12/3.281</f>
+        <v>5.9941074875546079</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" ref="G11:G15" si="0">PRODUCT(C11:F11)</f>
+        <v>8.9911612313319118</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="15">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <f>28.75/3.281</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E12" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <f t="shared" si="0"/>
+        <v>18.027236698767414</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <f>32.25/3.281</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E13" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>20.221856818617361</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="15">
+        <v>-2</v>
+      </c>
+      <c r="D14" s="3">
+        <f>42/12/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>-1.600121914050594</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="3">
+        <f>35/12/3.281</f>
+        <v>0.88895661891699673</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.66671746418774758</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="2">
+        <f>SUM(G10:G15)</f>
+        <v>65.698803971514621</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="2">
+        <f>1.15*9949.51</f>
+        <v>11441.9365</v>
+      </c>
       <c r="J16" s="22">
-        <f>0.13*G14*264/10</f>
-        <v>233.25808797635213</v>
-      </c>
-      <c r="K16" s="26"/>
+        <f>G16*I16</f>
+        <v>751721.54316801811</v>
+      </c>
+      <c r="K16" s="20"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
@@ -5526,93 +7742,124 @@
         <v>34</v>
       </c>
       <c r="I22" s="2">
-        <v>2808.56</v>
+        <f>1.15*2808.56</f>
+        <v>3229.8439999999996</v>
       </c>
       <c r="J22" s="22">
         <f>G22*I22</f>
-        <v>72585.993834379318</v>
+        <v>83473.892909536211</v>
       </c>
       <c r="K22" s="20"/>
     </row>
-    <row r="23" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="22">
-        <f>0.13*G22*24855.6/10</f>
-        <v>8350.9661778802583</v>
-      </c>
-      <c r="K23" s="26"/>
-    </row>
-    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="22">
-        <f>0.13*G22*50/10</f>
-        <v>16.798963167013188</v>
-      </c>
-      <c r="K24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="22">
-        <f>0.13*G22*300/10</f>
-        <v>100.79377900207912</v>
-      </c>
-      <c r="K25" s="26"/>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>3</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="13"/>
+      <c r="B25" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <f>(48.5/3.281)</f>
+        <v>14.782078634562632</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" ref="F25:F27" si="2">2.75/3.281</f>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G25" s="3">
+        <f>PRODUCT(C25:F25)</f>
+        <v>5.6992774985436547</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="B26" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="3">
+        <f>-5*2</f>
+        <v>-10</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" ref="G26:G27" si="3">PRODUCT(C26:F26)</f>
+        <v>-0.67471807375800064</v>
+      </c>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>3</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="3">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8381590978360256</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="3"/>
+        <v>1.0267448948491313</v>
+      </c>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
@@ -5621,25 +7868,25 @@
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3">
-        <f>(48.5/3.281)</f>
-        <v>14.782078634562632</v>
+        <f>((19.17-0.75)/3.281)</f>
+        <v>5.6141420298689431</v>
       </c>
       <c r="E28" s="3">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" ref="F28:F30" si="2">2.75/3.281</f>
-        <v>0.8381590978360256</v>
+        <f>(7.5+2.75)/3.281</f>
+        <v>3.1240475464797317</v>
       </c>
       <c r="G28" s="3">
         <f>PRODUCT(C28:F28)</f>
-        <v>5.6992774985436547</v>
+        <v>1.7538846634000815</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
@@ -5649,181 +7896,169 @@
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="16" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="C29" s="3">
-        <f>-5*2</f>
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="D29" s="3">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="E29" s="3">
         <v>0.23</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="2"/>
-        <v>0.8381590978360256</v>
+        <f>(7.5+2.75)/3.281</f>
+        <v>3.1240475464797317</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" ref="G29" si="3">PRODUCT(C29:F29)</f>
-        <v>-0.67471807375800064</v>
+        <f>PRODUCT(C29:F29)</f>
+        <v>0.16526211520877782</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="3">
-        <f>5*2</f>
-        <v>10</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F30" s="3">
-        <f t="shared" si="2"/>
-        <v>0.8381590978360256</v>
-      </c>
-      <c r="G30" s="3">
-        <f t="shared" ref="G30" si="4">PRODUCT(C30:F30)</f>
-        <v>1.0267448948491313</v>
-      </c>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="3">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3">
-        <f>((19.17-0.75)/3.281)</f>
-        <v>5.6141420298689431</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F31" s="3">
-        <f>(7.5+2.75)/3.281</f>
-        <v>3.1240475464797317</v>
-      </c>
-      <c r="G31" s="3">
-        <f>PRODUCT(C31:F31)</f>
-        <v>1.7538846634000815</v>
-      </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C32" s="3">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F32" s="3">
-        <f>(7.5+2.75)/3.281</f>
-        <v>3.1240475464797317</v>
-      </c>
-      <c r="G32" s="3">
-        <f>PRODUCT(C32:F32)</f>
-        <v>0.16526211520877782</v>
-      </c>
+    <row r="30" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="2">
+        <f>SUM(G25:G29)</f>
+        <v>7.9704510982436449</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="2">
+        <f>1.15*14491.84</f>
+        <v>16665.615999999998</v>
+      </c>
+      <c r="J30" s="22">
+        <f>G30*I30</f>
+        <v>132832.47735010684</v>
+      </c>
+      <c r="K30" s="20"/>
+    </row>
+    <row r="31" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="26"/>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
+        <v>4</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
     </row>
-    <row r="33" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
+      <c r="B33" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="3">
+        <f>(11.33-0.75)/3.281</f>
+        <v>3.2246266382200548</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G33" s="3">
+        <f>PRODUCT(C33:F33)</f>
+        <v>1.3759455329192551</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="3">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F34" s="3">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G34" s="3">
+        <f>PRODUCT(C34:F34)</f>
+        <v>0.11286193233770191</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="2">
-        <f>SUM(G28:G32)</f>
-        <v>7.9704510982436449</v>
-      </c>
-      <c r="H33" s="21" t="s">
+      <c r="C35" s="19"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="2">
+        <f>SUM(G33:G34)</f>
+        <v>1.488807465256957</v>
+      </c>
+      <c r="H35" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I33" s="2">
-        <f>14491.84</f>
-        <v>14491.84</v>
-      </c>
-      <c r="J33" s="22">
-        <f>G33*I33</f>
-        <v>115506.50204357118</v>
-      </c>
-      <c r="K33" s="20"/>
-    </row>
-    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="22">
-        <f>0.13*G33*8481.2</f>
-        <v>8787.8686810751205</v>
-      </c>
-      <c r="K34" s="26"/>
-    </row>
-    <row r="35" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="2">
+        <f>1.15*14827.62</f>
+        <v>17051.762999999999</v>
+      </c>
       <c r="J35" s="22">
-        <f>0.13*G33*912.17</f>
-        <v>945.15282917703769</v>
-      </c>
-      <c r="K35" s="26"/>
+        <f>G35*I35</f>
+        <v>25386.792050192362</v>
+      </c>
+      <c r="K35" s="20"/>
     </row>
     <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
-      <c r="B36" s="25" t="s">
-        <v>31</v>
-      </c>
+      <c r="B36" s="25"/>
       <c r="C36" s="26"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
@@ -5831,55 +8066,71 @@
       <c r="G36" s="27"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="22">
-        <f>0.13*G33*953.37</f>
-        <v>987.8425652592307</v>
-      </c>
+      <c r="J36" s="22"/>
       <c r="K36" s="26"/>
     </row>
-    <row r="37" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="22">
-        <f>0.13*G33*28</f>
-        <v>29.012441997606867</v>
-      </c>
-      <c r="K37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="26"/>
-    </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="13">
-        <v>4</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+    <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
+        <v>5</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="15">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3">
+        <f>19.17/3.281</f>
+        <v>5.8427308747333129</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="3">
+        <f>F28</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" ref="G38:G39" si="4">PRODUCT(C38:F38)</f>
+        <v>18.252969053951983</v>
+      </c>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="13"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3">
+        <f>19.17/3.281</f>
+        <v>5.8427308747333129</v>
+      </c>
       <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+      <c r="F39" s="3">
+        <f>F38-2.5/3.281</f>
+        <v>2.3620847302651629</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="4"/>
+        <v>13.801025382256377</v>
+      </c>
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
       <c r="J39" s="15"/>
@@ -5888,26 +8139,23 @@
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="3">
-        <f>2*2</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" s="3">
-        <f>(11.33-0.75)/3.281</f>
-        <v>3.2246266382200548</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0.1</v>
-      </c>
+        <f>(48.5)/3.281</f>
+        <v>14.782078634562632</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="F40" s="3">
         <f>3.5/3.281</f>
         <v>1.0667479427003961</v>
       </c>
       <c r="G40" s="3">
         <f>PRODUCT(C40:F40)</f>
-        <v>1.3759455329192551</v>
+        <v>31.537503944510334</v>
       </c>
       <c r="H40" s="15"/>
       <c r="I40" s="15"/>
@@ -5916,77 +8164,86 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
-      <c r="B41" s="16"/>
+      <c r="B41" s="16" t="s">
+        <v>103</v>
+      </c>
       <c r="C41" s="3">
         <v>2</v>
       </c>
       <c r="D41" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0.23</v>
-      </c>
+        <f>(48.5-0.75*2)/3.281</f>
+        <v>14.324900944833891</v>
+      </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="3">
         <f>3.5/3.281</f>
         <v>1.0667479427003961</v>
       </c>
       <c r="G41" s="3">
         <f>PRODUCT(C41:F41)</f>
-        <v>0.11286193233770191</v>
+        <v>30.562117224577026</v>
       </c>
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="18" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="13"/>
+      <c r="B42" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="3">
+        <f>C33</f>
+        <v>4</v>
+      </c>
+      <c r="D42" s="3">
+        <f>D33</f>
+        <v>3.2246266382200548</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
+        <f>F33</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="G42" s="3">
+        <f>PRODUCT(C42:F42)</f>
+        <v>13.759455329192551</v>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="2">
-        <f>SUM(G40:G41)</f>
-        <v>1.488807465256957</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" s="2">
-        <v>14827.62</v>
-      </c>
-      <c r="J42" s="22">
-        <f>G42*I42</f>
-        <v>22075.47134799336</v>
-      </c>
-      <c r="K42" s="20"/>
-    </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="2">
+        <f>SUM(G38:G42)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="2">
+        <f>1.15*415.5</f>
+        <v>477.82499999999999</v>
+      </c>
       <c r="J43" s="22">
-        <f>0.13*G42*8481.2</f>
-        <v>1641.4936036638496</v>
-      </c>
-      <c r="K43" s="26"/>
+        <f>G43*I43</f>
+        <v>51563.56311927185</v>
+      </c>
+      <c r="K43" s="20"/>
     </row>
     <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="24"/>
-      <c r="B44" s="25" t="s">
-        <v>32</v>
-      </c>
+      <c r="B44" s="25"/>
       <c r="C44" s="26"/>
       <c r="D44" s="27"/>
       <c r="E44" s="27"/>
@@ -5994,122 +8251,134 @@
       <c r="G44" s="27"/>
       <c r="H44" s="26"/>
       <c r="I44" s="26"/>
-      <c r="J44" s="22">
-        <f>0.13*G42*1303.1</f>
-        <v>252.20845103692426</v>
-      </c>
+      <c r="J44" s="22"/>
       <c r="K44" s="26"/>
     </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="22">
-        <f>0.13*G42*889.81</f>
-        <v>172.21825018583806</v>
-      </c>
-      <c r="K45" s="26"/>
-    </row>
-    <row r="46" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="22">
-        <f>0.13*G42*36.4</f>
-        <v>7.0450369255959204</v>
-      </c>
-      <c r="K46" s="26"/>
-    </row>
-    <row r="47" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="26"/>
-    </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
-        <v>5</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
-      <c r="B49" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C49" s="15">
+    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>6</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="13"/>
+      <c r="B46" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="3">
         <v>1</v>
       </c>
-      <c r="D49" s="3">
-        <f>19.17/3.281</f>
-        <v>5.8427308747333129</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="3">
-        <f>F31</f>
-        <v>3.1240475464797317</v>
-      </c>
-      <c r="G49" s="3">
-        <f t="shared" ref="G49:G50" si="5">PRODUCT(C49:F49)</f>
-        <v>18.252969053951983</v>
-      </c>
+      <c r="D46" s="3">
+        <f>G43</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3">
+        <f>PRODUCT(C46:F46)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="2">
+        <f>SUM(G46:G46)</f>
+        <v>107.91307093448826</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="2">
+        <f>1.15*253.8</f>
+        <v>291.87</v>
+      </c>
+      <c r="J47" s="22">
+        <f>G47*I47</f>
+        <v>31496.588013649089</v>
+      </c>
+      <c r="K47" s="20"/>
+    </row>
+    <row r="48" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="26"/>
+    </row>
+    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>7</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="G49" s="15"/>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="15">
-        <v>1</v>
+      <c r="B50" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="3">
+        <v>30</v>
       </c>
       <c r="D50" s="3">
-        <f>19.17/3.281</f>
-        <v>5.8427308747333129</v>
-      </c>
-      <c r="E50" s="15"/>
+        <v>0.3</v>
+      </c>
+      <c r="E50" s="3">
+        <v>10.5</v>
+      </c>
       <c r="F50" s="3">
-        <f>F49-2.5/3.281</f>
-        <v>2.3620847302651629</v>
+        <f>PRODUCT(C50:E50)</f>
+        <v>94.5</v>
       </c>
       <c r="G50" s="3">
-        <f t="shared" si="5"/>
-        <v>13.801025382256377</v>
+        <f>F50</f>
+        <v>94.5</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
@@ -6118,50 +8387,52 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
-      <c r="B51" s="16" t="s">
-        <v>102</v>
-      </c>
+      <c r="B51" s="16"/>
       <c r="C51" s="3">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D51" s="3">
-        <f>(48.5)/3.281</f>
-        <v>14.782078634562632</v>
-      </c>
-      <c r="E51" s="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="E51" s="3">
+        <v>10.5</v>
+      </c>
       <c r="F51" s="3">
-        <f>3.5/3.281</f>
-        <v>1.0667479427003961</v>
+        <f>PRODUCT(C51:E51)</f>
+        <v>103.95</v>
       </c>
       <c r="G51" s="3">
-        <f>PRODUCT(C51:F51)</f>
-        <v>31.537503944510334</v>
+        <f>F51</f>
+        <v>103.95</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
-      <c r="B52" s="16" t="s">
-        <v>103</v>
+      <c r="B52" s="50" t="s">
+        <v>110</v>
       </c>
       <c r="C52" s="3">
-        <v>2</v>
+        <f>2*2</f>
+        <v>4</v>
       </c>
       <c r="D52" s="3">
-        <f>(48.5-0.75*2)/3.281</f>
-        <v>14.324900944833891</v>
-      </c>
-      <c r="E52" s="3"/>
+        <f>28.75/3.281</f>
+        <v>8.7625723864675393</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5.8</v>
+      </c>
       <c r="F52" s="3">
-        <f>3.5/3.281</f>
-        <v>1.0667479427003961</v>
+        <f t="shared" ref="F52:F57" si="5">PRODUCT(C52:E52)</f>
+        <v>203.29167936604691</v>
       </c>
       <c r="G52" s="3">
-        <f>PRODUCT(C52:F52)</f>
-        <v>30.562117224577026</v>
+        <f t="shared" ref="G52:G57" si="6">F52</f>
+        <v>203.29167936604691</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15"/>
@@ -6170,1002 +8441,522 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
-      <c r="B53" s="16" t="s">
-        <v>92</v>
-      </c>
+      <c r="B53" s="16"/>
       <c r="C53" s="3">
-        <f>C40</f>
+        <f>2*2</f>
         <v>4</v>
       </c>
       <c r="D53" s="3">
-        <f>D40</f>
-        <v>3.2246266382200548</v>
-      </c>
-      <c r="E53" s="3"/>
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E53" s="3">
+        <v>5.8</v>
+      </c>
       <c r="F53" s="3">
-        <f>F40</f>
-        <v>1.0667479427003961</v>
+        <f t="shared" si="5"/>
+        <v>47.729350807680582</v>
       </c>
       <c r="G53" s="3">
-        <f>PRODUCT(C53:F53)</f>
-        <v>13.759455329192551</v>
+        <f t="shared" si="6"/>
+        <v>47.729350807680582</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
     </row>
-    <row r="54" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="18" t="s">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="3">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F54" s="3">
+        <f t="shared" si="5"/>
+        <v>95.458701615361164</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="6"/>
+        <v>95.458701615361164</v>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="13"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="3">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D55" s="3">
+        <f>32.25/3.281</f>
+        <v>9.8293203291679365</v>
+      </c>
+      <c r="E55" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F55" s="3">
+        <f t="shared" si="5"/>
+        <v>228.04023163669612</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="6"/>
+        <v>228.04023163669612</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="13"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="3">
+        <f>2*2+1</f>
+        <v>5</v>
+      </c>
+      <c r="D56" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E56" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F56" s="3">
+        <f t="shared" si="5"/>
+        <v>59.661688509600722</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="6"/>
+        <v>59.661688509600722</v>
+      </c>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="13"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="3">
+        <v>9</v>
+      </c>
+      <c r="D57" s="3">
+        <f>6.75/3.281</f>
+        <v>2.0572996037793354</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F57" s="3">
+        <f t="shared" si="5"/>
+        <v>107.3910393172813</v>
+      </c>
+      <c r="G57" s="3">
+        <f t="shared" si="6"/>
+        <v>107.3910393172813</v>
+      </c>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+    </row>
+    <row r="58" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="17"/>
+      <c r="B58" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="2">
-        <f>SUM(G49:G53)</f>
-        <v>107.91307093448826</v>
-      </c>
-      <c r="H54" s="21" t="s">
+      <c r="C58" s="19"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="2">
+        <f>SUM(G50:G57)</f>
+        <v>940.02269125266685</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I58" s="2">
+        <f>1.15*182.51</f>
+        <v>209.88649999999998</v>
+      </c>
+      <c r="J58" s="22">
+        <f>G58*I58</f>
+        <v>197298.07258760286</v>
+      </c>
+      <c r="K58" s="20"/>
+    </row>
+    <row r="59" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="24"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="26"/>
+    </row>
+    <row r="60" spans="1:11" ht="138.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="13">
+        <v>8</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="13"/>
+      <c r="B61" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3">
+        <f>(48.5+5+5)/3.281</f>
+        <v>17.829929899420907</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G61" s="3">
+        <f>PRODUCT(C61:F61)</f>
+        <v>26.744894849131363</v>
+      </c>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="13"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3">
+        <f>(21.5+5)/3.281</f>
+        <v>8.076805851874429</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G62" s="3">
+        <f>PRODUCT(C62:F62)</f>
+        <v>12.115208777811644</v>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+    </row>
+    <row r="63" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="17"/>
+      <c r="B63" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="2">
+        <f>SUM(G61:G62)</f>
+        <v>38.860103626943008</v>
+      </c>
+      <c r="H63" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I54" s="2">
-        <v>415.5</v>
-      </c>
-      <c r="J54" s="22">
-        <f>G54*I54</f>
-        <v>44837.880973279869</v>
-      </c>
-      <c r="K54" s="20"/>
-    </row>
-    <row r="55" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="24"/>
-      <c r="B55" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="26"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="22">
-        <f>0.13*G54*7010.67/100</f>
-        <v>983.50580771077557</v>
-      </c>
-      <c r="K55" s="26"/>
-    </row>
-    <row r="56" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="24"/>
-      <c r="B56" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="26"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="22">
-        <f>0.13*G54*4639.73/100</f>
-        <v>650.89376638893521</v>
-      </c>
-      <c r="K56" s="26"/>
-    </row>
-    <row r="57" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="26"/>
-    </row>
-    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="13">
-        <v>6</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C59" s="3">
-        <v>1</v>
-      </c>
-      <c r="D59" s="3">
-        <f>G54</f>
-        <v>107.91307093448826</v>
-      </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3">
-        <f>PRODUCT(C59:F59)</f>
-        <v>107.91307093448826</v>
-      </c>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
-    </row>
-    <row r="60" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
-      <c r="B60" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="2">
-        <f>SUM(G59:G59)</f>
-        <v>107.91307093448826</v>
-      </c>
-      <c r="H60" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I60" s="2">
-        <v>253.8</v>
-      </c>
-      <c r="J60" s="22">
-        <f>G60*I60</f>
-        <v>27388.337403173122</v>
-      </c>
-      <c r="K60" s="20"/>
-    </row>
-    <row r="61" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
-      <c r="B61" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="26"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="22">
-        <f>0.13*G60*2304/100</f>
-        <v>323.22123006297926</v>
-      </c>
-      <c r="K61" s="26"/>
-    </row>
-    <row r="62" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
-      <c r="B62" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" s="26"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="22">
-        <f>0.13*G60*10432/100</f>
-        <v>1463.473902785156</v>
-      </c>
-      <c r="K62" s="26"/>
-    </row>
-    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="26"/>
-    </row>
-    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="13">
-        <v>7</v>
-      </c>
-      <c r="B64" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C64" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="F64" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-    </row>
-    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" s="3">
-        <v>30</v>
-      </c>
-      <c r="D65" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="E65" s="3">
-        <v>10.5</v>
-      </c>
-      <c r="F65" s="3">
-        <f>PRODUCT(C65:E65)</f>
-        <v>94.5</v>
-      </c>
-      <c r="G65" s="3">
-        <f>F65</f>
-        <v>94.5</v>
-      </c>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
+      <c r="I63" s="2">
+        <f>1.15*30571.1/10</f>
+        <v>3515.6764999999991</v>
+      </c>
+      <c r="J63" s="22">
+        <f>G63*I63</f>
+        <v>136619.55310880826</v>
+      </c>
+      <c r="K63" s="20"/>
+    </row>
+    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="24"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="17">
+        <v>9</v>
+      </c>
+      <c r="B65" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="20"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="13"/>
-      <c r="B66" s="16"/>
+      <c r="B66" s="16" t="s">
+        <v>121</v>
+      </c>
       <c r="C66" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D66" s="3">
-        <v>0.3</v>
+        <f>D28</f>
+        <v>5.6141420298689431</v>
       </c>
       <c r="E66" s="3">
-        <v>10.5</v>
+        <v>0.1</v>
       </c>
       <c r="F66" s="3">
-        <f>PRODUCT(C66:E66)</f>
-        <v>103.95</v>
+        <f>7.5/3.281</f>
+        <v>2.2858884486437061</v>
       </c>
       <c r="G66" s="3">
-        <f>F66</f>
-        <v>103.95</v>
+        <f>PRODUCT(C66:F66)</f>
+        <v>1.2833302415122547</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
-      <c r="B67" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C67" s="3">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D67" s="3">
-        <f>28.75/3.281</f>
-        <v>8.7625723864675393</v>
-      </c>
-      <c r="E67" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="F67" s="3">
-        <f t="shared" ref="F67:F71" si="6">PRODUCT(C67:E67)</f>
-        <v>203.29167936604691</v>
-      </c>
-      <c r="G67" s="3">
-        <f t="shared" ref="G67:G72" si="7">F67</f>
-        <v>203.29167936604691</v>
-      </c>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="3">
-        <f>2*2+2</f>
-        <v>6</v>
-      </c>
-      <c r="D68" s="3">
-        <f>6.75/3.281</f>
-        <v>2.0572996037793354</v>
-      </c>
-      <c r="E68" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="F68" s="3">
-        <f t="shared" si="6"/>
-        <v>71.59402621152087</v>
-      </c>
-      <c r="G68" s="3">
-        <f t="shared" si="7"/>
-        <v>71.59402621152087</v>
-      </c>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="3">
-        <v>8</v>
-      </c>
-      <c r="D69" s="3">
-        <f>6.75/3.281</f>
-        <v>2.0572996037793354</v>
-      </c>
-      <c r="E69" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="F69" s="3">
-        <f t="shared" ref="F69" si="8">PRODUCT(C69:E69)</f>
-        <v>95.458701615361164</v>
-      </c>
-      <c r="G69" s="3">
-        <f t="shared" si="7"/>
-        <v>95.458701615361164</v>
-      </c>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="3">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D70" s="3">
-        <f>32.25/3.281</f>
-        <v>9.8293203291679365</v>
-      </c>
-      <c r="E70" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="F70" s="3">
-        <f t="shared" si="6"/>
-        <v>228.04023163669612</v>
-      </c>
-      <c r="G70" s="3">
-        <f t="shared" si="7"/>
-        <v>228.04023163669612</v>
-      </c>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="3">
-        <f>2*2+2</f>
-        <v>6</v>
-      </c>
-      <c r="D71" s="3">
-        <f>6.75/3.281</f>
-        <v>2.0572996037793354</v>
-      </c>
-      <c r="E71" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="F71" s="3">
-        <f t="shared" si="6"/>
-        <v>71.59402621152087</v>
-      </c>
-      <c r="G71" s="3">
-        <f t="shared" si="7"/>
-        <v>71.59402621152087</v>
-      </c>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="3">
-        <v>9</v>
-      </c>
-      <c r="D72" s="3">
-        <f>6.75/3.281</f>
-        <v>2.0572996037793354</v>
-      </c>
-      <c r="E72" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="F72" s="3">
-        <f t="shared" ref="F72" si="9">PRODUCT(C72:E72)</f>
-        <v>107.3910393172813</v>
-      </c>
-      <c r="G72" s="3">
-        <f t="shared" si="7"/>
-        <v>107.3910393172813</v>
-      </c>
-      <c r="H72" s="15"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-    </row>
-    <row r="73" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="18" t="s">
+    <row r="67" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="17"/>
+      <c r="B67" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="2">
-        <f>SUM(G65:G72)</f>
-        <v>975.8197043584272</v>
-      </c>
-      <c r="H73" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="I73" s="2">
-        <v>182.51</v>
-      </c>
+      <c r="C67" s="19"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="2">
+        <f>SUM(G65:G66)</f>
+        <v>1.2833302415122547</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" s="2">
+        <f>1.15*1982.2</f>
+        <v>2279.5299999999997</v>
+      </c>
+      <c r="J67" s="22">
+        <f>G67*I67</f>
+        <v>2925.3897854344295</v>
+      </c>
+      <c r="K67" s="20"/>
+    </row>
+    <row r="68" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="24"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="26"/>
+    </row>
+    <row r="69" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="17">
+        <v>10</v>
+      </c>
+      <c r="B69" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="19">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="21">
+        <f t="shared" ref="G69" si="7">PRODUCT(C69:F69)</f>
+        <v>1</v>
+      </c>
+      <c r="H69" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2">
+        <v>2000</v>
+      </c>
+      <c r="J69" s="21">
+        <f>G69*I69</f>
+        <v>2000</v>
+      </c>
+      <c r="K69" s="20"/>
+    </row>
+    <row r="70" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="24"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="26"/>
+    </row>
+    <row r="71" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="17">
+        <v>11</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="19">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="21">
+        <f t="shared" ref="G71" si="8">PRODUCT(C71:F71)</f>
+        <v>1</v>
+      </c>
+      <c r="H71" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="2">
+        <v>500</v>
+      </c>
+      <c r="J71" s="21">
+        <f>G71*I71</f>
+        <v>500</v>
+      </c>
+      <c r="K71" s="20"/>
+    </row>
+    <row r="72" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="17"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="20"/>
+    </row>
+    <row r="73" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="48"/>
+      <c r="B73" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="34"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
       <c r="J73" s="22">
-        <f>G73*I73</f>
-        <v>178096.85424245655</v>
-      </c>
-      <c r="K73" s="20"/>
-    </row>
-    <row r="74" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
-      <c r="B74" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="21">
-        <f>0.13*G73*1761.42/18.94</f>
-        <v>11797.660225693386</v>
-      </c>
-      <c r="K74" s="38"/>
-    </row>
-    <row r="75" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="24"/>
-      <c r="B75" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C75" s="26"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="22">
-        <f>0.13*G73*110/18.94</f>
-        <v>736.75933328012195</v>
-      </c>
-      <c r="K75" s="26"/>
+        <f>SUM(J9:J71)</f>
+        <v>1415817.87209262</v>
+      </c>
+      <c r="K73" s="36"/>
+    </row>
+    <row r="74" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="44"/>
+    </row>
+    <row r="75" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="37"/>
+      <c r="B75" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="60">
+        <f>J73</f>
+        <v>1415817.87209262</v>
+      </c>
+      <c r="D75" s="61"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="43"/>
     </row>
     <row r="76" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="24"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="26"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="26"/>
-    </row>
-    <row r="77" spans="1:11" ht="138.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="13">
-        <v>8</v>
-      </c>
-      <c r="B77" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="3">
-        <v>1</v>
-      </c>
-      <c r="D78" s="3">
-        <f>(48.5+5+5)/3.281</f>
-        <v>17.829929899420907</v>
-      </c>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G78" s="3">
-        <f>PRODUCT(C78:F78)</f>
-        <v>26.744894849131363</v>
-      </c>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="3">
-        <v>1</v>
-      </c>
-      <c r="D79" s="3">
-        <f>(21.5+5)/3.281</f>
-        <v>8.076805851874429</v>
-      </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G79" s="3">
-        <f>PRODUCT(C79:F79)</f>
-        <v>12.115208777811644</v>
-      </c>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
-    </row>
-    <row r="80" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
-      <c r="B80" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" s="19"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="2">
-        <f>SUM(G78:G79)</f>
-        <v>38.860103626943008</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I80" s="2">
-        <f>30571.1/10</f>
-        <v>3057.1099999999997</v>
-      </c>
-      <c r="J80" s="22">
-        <f>G80*I80</f>
-        <v>118799.61139896372</v>
-      </c>
-      <c r="K80" s="20"/>
-    </row>
-    <row r="81" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
-      <c r="B81" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C81" s="26"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="22">
-        <f>0.13*G80*3302.43/10</f>
-        <v>1668.3260362694302</v>
-      </c>
-      <c r="K81" s="26"/>
-    </row>
-    <row r="82" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
-      <c r="B82" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="C82" s="26"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="26"/>
-      <c r="I82" s="26"/>
-      <c r="J82" s="22">
-        <f>0.13*G80*2981.58/10</f>
-        <v>1506.2386010362693</v>
-      </c>
-      <c r="K82" s="26"/>
-    </row>
-    <row r="83" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="24"/>
-      <c r="B83" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" s="26"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="26"/>
-      <c r="I83" s="26"/>
-      <c r="J83" s="22">
-        <f>0.13*G80*2273.04/10</f>
-        <v>1148.2974093264249</v>
-      </c>
-      <c r="K83" s="26"/>
-    </row>
-    <row r="84" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="24"/>
-      <c r="B84" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C84" s="26"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="26"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="22">
-        <f>0.13*G80*6383.04/10</f>
-        <v>3224.59274611399</v>
-      </c>
-      <c r="K84" s="26"/>
-    </row>
-    <row r="85" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="24"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="26"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="26"/>
-      <c r="I85" s="26"/>
-      <c r="J85" s="22"/>
-      <c r="K85" s="26"/>
-    </row>
-    <row r="86" spans="1:11" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A86" s="17">
-        <v>9</v>
-      </c>
-      <c r="B86" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C86" s="19"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="20"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
-      <c r="B87" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C87" s="3">
-        <v>1</v>
-      </c>
-      <c r="D87" s="3">
-        <f>D31</f>
-        <v>5.6141420298689431</v>
-      </c>
-      <c r="E87" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F87" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G87" s="3">
-        <f>PRODUCT(C87:F87)</f>
-        <v>1.2833302415122547</v>
-      </c>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-    </row>
-    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
-      <c r="B88" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" s="19"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="2">
-        <f>SUM(G86:G87)</f>
-        <v>1.2833302415122547</v>
-      </c>
-      <c r="H88" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I88" s="2">
-        <v>1982.2</v>
-      </c>
-      <c r="J88" s="22">
-        <f>G88*I88</f>
-        <v>2543.8172047255912</v>
-      </c>
-      <c r="K88" s="20"/>
-    </row>
-    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="24"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="26"/>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
-      <c r="H89" s="26"/>
-      <c r="I89" s="26"/>
-      <c r="J89" s="22"/>
-      <c r="K89" s="26"/>
-    </row>
-    <row r="90" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="17">
-        <v>10</v>
-      </c>
-      <c r="B90" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C90" s="19">
-        <v>1</v>
-      </c>
-      <c r="D90" s="1"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="21">
-        <f t="shared" ref="G90" si="10">PRODUCT(C90:F90)</f>
-        <v>1</v>
-      </c>
-      <c r="H90" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J90" s="21">
-        <f>G90*I90</f>
-        <v>5000</v>
-      </c>
-      <c r="K90" s="20"/>
-    </row>
-    <row r="91" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="26"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="26"/>
-      <c r="I91" s="26"/>
-      <c r="J91" s="22"/>
-      <c r="K91" s="26"/>
-    </row>
-    <row r="92" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="17">
-        <v>11</v>
-      </c>
-      <c r="B92" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" s="19">
-        <v>1</v>
-      </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="21">
-        <f t="shared" ref="G92" si="11">PRODUCT(C92:F92)</f>
-        <v>1</v>
-      </c>
-      <c r="H92" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" s="2">
-        <v>500</v>
-      </c>
-      <c r="J92" s="21">
-        <f>G92*I92</f>
-        <v>500</v>
-      </c>
-      <c r="K92" s="20"/>
-    </row>
-    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="17"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="20"/>
-      <c r="F93" s="20"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="21"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="20"/>
-    </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="48"/>
-      <c r="B94" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C94" s="34"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="35"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="22"/>
-      <c r="H94" s="22"/>
-      <c r="I94" s="22"/>
-      <c r="J94" s="22">
-        <f>SUM(J9:J92)</f>
-        <v>1388575.8699169443</v>
-      </c>
-      <c r="K94" s="36"/>
-    </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="44"/>
-    </row>
-    <row r="96" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="37"/>
-      <c r="B96" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C96" s="54">
-        <f>J94</f>
-        <v>1388575.8699169443</v>
-      </c>
-      <c r="D96" s="55"/>
-      <c r="E96" s="39">
-        <v>100</v>
-      </c>
-      <c r="F96" s="37"/>
-      <c r="G96" s="40"/>
-      <c r="H96" s="37"/>
-      <c r="I96" s="41"/>
-      <c r="J96" s="42"/>
-      <c r="K96" s="43"/>
-    </row>
-    <row r="97" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="44"/>
-      <c r="B97" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C97" s="56">
-        <v>1200000</v>
-      </c>
-      <c r="D97" s="57"/>
-      <c r="E97" s="39"/>
-    </row>
-    <row r="98" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="44"/>
-      <c r="B98" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C98" s="56">
-        <f>C97-C100-C101</f>
-        <v>1140000</v>
-      </c>
-      <c r="D98" s="57"/>
-      <c r="E98" s="39">
-        <f>C98/C96*100</f>
-        <v>82.098502840049164</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="44"/>
-      <c r="B99" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C99" s="58">
-        <f>C96-C98</f>
-        <v>248575.8699169443</v>
-      </c>
-      <c r="D99" s="58"/>
-      <c r="E99" s="39">
-        <f>100-E98</f>
-        <v>17.901497159950836</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="44"/>
-      <c r="B100" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C100" s="54">
-        <f>C97*0.03</f>
-        <v>36000</v>
-      </c>
-      <c r="D100" s="55"/>
-      <c r="E100" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="44"/>
-      <c r="B101" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C101" s="54">
-        <f>C97*0.02</f>
-        <v>24000</v>
-      </c>
-      <c r="D101" s="55"/>
-      <c r="E101" s="39">
-        <v>2</v>
-      </c>
+      <c r="A76" s="44"/>
+      <c r="B76" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" s="64">
+        <f>0.13*C75</f>
+        <v>184056.32337204061</v>
+      </c>
+      <c r="D76" s="65"/>
+    </row>
+    <row r="77" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="44"/>
+      <c r="B77" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="64">
+        <f>SUM(C75:D76)</f>
+        <v>1599874.1954646606</v>
+      </c>
+      <c r="D77" s="65"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
+  <mergeCells count="12">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
